--- a/data/New Microsoft Excel Worksheet.xlsx
+++ b/data/New Microsoft Excel Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\berkercin\Desktop\Projects\Scheduling\Campus-Scheduling\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F9A0BD-8559-49BA-862C-91FA34A14C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B795BBC-29DB-4232-997E-53A36DCE9072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1235,14 +1235,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V1542"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="16" max="16" width="5.42578125" customWidth="1"/>
-    <col min="17" max="17" width="3.5703125" customWidth="1"/>
-    <col min="18" max="18" width="1.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" customWidth="1"/>
+    <col min="17" max="17" width="3.54296875" customWidth="1"/>
+    <col min="18" max="18" width="1.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>53</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A3" s="23"/>
       <c r="B3" s="25"/>
       <c r="C3" s="23"/>
@@ -1402,7 +1402,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A4" s="23"/>
       <c r="B4" s="25"/>
       <c r="C4" s="23"/>
@@ -1452,7 +1452,7 @@
         <v>102.98</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="23"/>
       <c r="B5" s="25"/>
       <c r="C5" s="23"/>
@@ -1504,7 +1504,7 @@
         <v>127.374</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A6" s="23"/>
       <c r="B6" s="25"/>
       <c r="C6" s="23"/>
@@ -1554,7 +1554,7 @@
         <v>124.93300000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A7" s="23"/>
       <c r="B7" s="25"/>
       <c r="C7" s="23"/>
@@ -1604,7 +1604,7 @@
         <v>120.69</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A8" s="23"/>
       <c r="B8" s="25"/>
       <c r="C8" s="23"/>
@@ -1654,7 +1654,7 @@
         <v>100.479</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A9" s="23"/>
       <c r="B9" s="25"/>
       <c r="C9" s="23"/>
@@ -1704,7 +1704,7 @@
         <v>73.364999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A10" s="23"/>
       <c r="B10" s="25"/>
       <c r="C10" s="23"/>
@@ -1756,7 +1756,7 @@
         <v>48.91</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A11" s="23"/>
       <c r="B11" s="25"/>
       <c r="C11" s="23"/>
@@ -1808,7 +1808,7 @@
         <v>73.364999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A12" s="23"/>
       <c r="B12" s="25"/>
       <c r="C12" s="23"/>
@@ -1860,7 +1860,7 @@
         <v>73.912999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A13" s="23"/>
       <c r="B13" s="25"/>
       <c r="C13" s="23"/>
@@ -1912,7 +1912,7 @@
         <v>68.674999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A14" s="23"/>
       <c r="B14" s="25"/>
       <c r="C14" s="23"/>
@@ -1964,7 +1964,7 @@
         <v>52.563000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A15" s="23"/>
       <c r="B15" s="25"/>
       <c r="C15" s="23"/>
@@ -2016,7 +2016,7 @@
         <v>68.674999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A16" s="23"/>
       <c r="B16" s="25"/>
       <c r="C16" s="23"/>
@@ -2068,7 +2068,7 @@
         <v>86.094999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A17" s="23"/>
       <c r="B17" s="25"/>
       <c r="C17" s="23"/>
@@ -2120,7 +2120,7 @@
         <v>74.034999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A18" s="23"/>
       <c r="B18" s="25"/>
       <c r="C18" s="23"/>
@@ -2172,7 +2172,7 @@
         <v>68.608000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A19" s="23"/>
       <c r="B19" s="25"/>
       <c r="C19" s="23"/>
@@ -2224,7 +2224,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A20" s="23"/>
       <c r="B20" s="25"/>
       <c r="C20" s="23"/>
@@ -2276,7 +2276,7 @@
         <v>68.674999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A21" s="23"/>
       <c r="B21" s="25"/>
       <c r="C21" s="23"/>
@@ -2328,7 +2328,7 @@
         <v>73.364999999999995</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A22" s="23"/>
       <c r="B22" s="25"/>
       <c r="C22" s="23"/>
@@ -2380,7 +2380,7 @@
         <v>78.724999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="23"/>
       <c r="B23" s="25"/>
       <c r="C23" s="23" t="s">
@@ -2434,7 +2434,7 @@
         <v>124.023</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A24" s="23"/>
       <c r="B24" s="25"/>
       <c r="C24" s="23"/>
@@ -2486,7 +2486,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A25" s="23"/>
       <c r="B25" s="25"/>
       <c r="C25" s="23"/>
@@ -2538,7 +2538,7 @@
         <v>49.298000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A26" s="23"/>
       <c r="B26" s="25"/>
       <c r="C26" s="23"/>
@@ -2590,7 +2590,7 @@
         <v>99.665999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A27" s="23"/>
       <c r="B27" s="25"/>
       <c r="C27" s="23"/>
@@ -2642,7 +2642,7 @@
         <v>72.840999999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A28" s="23"/>
       <c r="B28" s="25"/>
       <c r="C28" s="23"/>
@@ -2694,7 +2694,7 @@
         <v>126.027</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A29" s="23"/>
       <c r="B29" s="25"/>
       <c r="C29" s="23"/>
@@ -2744,7 +2744,7 @@
         <v>74.894000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A30" s="23"/>
       <c r="B30" s="25"/>
       <c r="C30" s="23"/>
@@ -2796,7 +2796,7 @@
         <v>74.605000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A31" s="23"/>
       <c r="B31" s="25"/>
       <c r="C31" s="23" t="s">
@@ -2848,7 +2848,7 @@
         <v>150.03299999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A32" s="23"/>
       <c r="B32" s="25"/>
       <c r="C32" s="23"/>
@@ -2898,7 +2898,7 @@
         <v>121.125</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A33" s="23"/>
       <c r="B33" s="25"/>
       <c r="C33" s="23"/>
@@ -2950,7 +2950,7 @@
         <v>92.14</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A34" s="23"/>
       <c r="B34" s="25"/>
       <c r="C34" s="23"/>
@@ -3002,7 +3002,7 @@
         <v>90.44</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A35" s="23"/>
       <c r="B35" s="25"/>
       <c r="C35" s="23"/>
@@ -3052,7 +3052,7 @@
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A36" s="23"/>
       <c r="B36" s="25"/>
       <c r="C36" s="23"/>
@@ -3102,7 +3102,7 @@
         <v>153.09800000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A37" s="23"/>
       <c r="B37" s="25"/>
       <c r="C37" s="23"/>
@@ -3154,7 +3154,7 @@
         <v>92.14</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="23"/>
       <c r="B38" s="25"/>
       <c r="C38" s="23"/>
@@ -3206,7 +3206,7 @@
         <v>89.896000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A39" s="23"/>
       <c r="B39" s="25"/>
       <c r="C39" s="23"/>
@@ -3258,7 +3258,7 @@
         <v>76.364000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A40" s="23"/>
       <c r="B40" s="25"/>
       <c r="C40" s="23"/>
@@ -3310,7 +3310,7 @@
         <v>75.98</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A41" s="23"/>
       <c r="B41" s="25"/>
       <c r="C41" s="23"/>
@@ -3362,7 +3362,7 @@
         <v>75.795000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A42" s="23"/>
       <c r="B42" s="25"/>
       <c r="C42" s="23"/>
@@ -3414,7 +3414,7 @@
         <v>75.594999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A43" s="23"/>
       <c r="B43" s="25"/>
       <c r="C43" s="23"/>
@@ -3466,7 +3466,7 @@
         <v>92.751999999999995</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="23"/>
       <c r="B44" s="25"/>
       <c r="C44" s="23"/>
@@ -3516,7 +3516,7 @@
         <v>55.054000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A45" s="23"/>
       <c r="B45" s="25"/>
       <c r="C45" s="23" t="s">
@@ -3568,7 +3568,7 @@
         <v>36.670999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A46" s="23"/>
       <c r="B46" s="25"/>
       <c r="C46" s="23"/>
@@ -3618,7 +3618,7 @@
         <v>99.364000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A47" s="23"/>
       <c r="B47" s="25"/>
       <c r="C47" s="23"/>
@@ -3668,7 +3668,7 @@
         <v>69.915000000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23"/>
       <c r="B48" s="25"/>
       <c r="C48" s="23"/>
@@ -3718,7 +3718,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="23"/>
       <c r="B49" s="25"/>
       <c r="C49" s="23"/>
@@ -3768,7 +3768,7 @@
         <v>80.69</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23"/>
       <c r="B50" s="25"/>
       <c r="C50" s="23"/>
@@ -3818,7 +3818,7 @@
         <v>80.376000000000005</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="23"/>
       <c r="B51" s="25"/>
       <c r="C51" s="23"/>
@@ -3868,7 +3868,7 @@
         <v>87.132999999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="23"/>
       <c r="B52" s="25"/>
       <c r="C52" s="23"/>
@@ -3918,7 +3918,7 @@
         <v>58.591999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="23"/>
       <c r="B53" s="25"/>
       <c r="C53" s="23"/>
@@ -3968,7 +3968,7 @@
         <v>34.965000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="23"/>
       <c r="B54" s="25"/>
       <c r="C54" s="23"/>
@@ -4018,7 +4018,7 @@
         <v>49.56</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="23"/>
       <c r="B55" s="25"/>
       <c r="C55" s="23"/>
@@ -4068,7 +4068,7 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="23"/>
       <c r="B56" s="25"/>
       <c r="C56" s="23"/>
@@ -4118,7 +4118,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A57" s="23"/>
       <c r="B57" s="25"/>
       <c r="C57" s="23"/>
@@ -4168,7 +4168,7 @@
         <v>68.045000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A58" s="23"/>
       <c r="B58" s="25"/>
       <c r="C58" s="23"/>
@@ -4218,7 +4218,7 @@
         <v>48.807000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A59" s="23"/>
       <c r="B59" s="25"/>
       <c r="C59" s="23"/>
@@ -4268,7 +4268,7 @@
         <v>80.775000000000006</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A60" s="23"/>
       <c r="B60" s="25"/>
       <c r="C60" s="23"/>
@@ -4318,7 +4318,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="42" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" ht="42" x14ac:dyDescent="0.35">
       <c r="A61" s="23"/>
       <c r="B61" s="25"/>
       <c r="C61" s="23"/>
@@ -4368,7 +4368,7 @@
         <v>59.128</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A62" s="23"/>
       <c r="B62" s="25"/>
       <c r="C62" s="23"/>
@@ -4418,7 +4418,7 @@
         <v>46.597000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A63" s="23"/>
       <c r="B63" s="25"/>
       <c r="C63" s="23"/>
@@ -4468,6129 +4468,6129 @@
         <v>36.345999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64" s="23"/>
       <c r="B64" s="25"/>
       <c r="C64" s="13"/>
       <c r="D64" s="15"/>
       <c r="E64" s="14"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="23"/>
       <c r="B65" s="25"/>
       <c r="C65" s="13"/>
       <c r="D65" s="15"/>
       <c r="E65" s="14"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="23"/>
       <c r="B66" s="25"/>
       <c r="C66" s="13"/>
       <c r="D66" s="15"/>
       <c r="E66" s="14"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="23"/>
       <c r="B67" s="25"/>
       <c r="C67" s="13"/>
       <c r="D67" s="15"/>
       <c r="E67" s="14"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="23"/>
       <c r="B68" s="25"/>
       <c r="C68" s="13"/>
       <c r="D68" s="15"/>
       <c r="E68" s="14"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="23"/>
       <c r="B69" s="25"/>
       <c r="C69" s="13"/>
       <c r="D69" s="15"/>
       <c r="E69" s="14"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="23"/>
       <c r="B70" s="25"/>
       <c r="C70" s="13"/>
       <c r="D70" s="15"/>
       <c r="E70" s="14"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="23"/>
       <c r="B71" s="25"/>
       <c r="C71" s="13"/>
       <c r="D71" s="15"/>
       <c r="E71" s="14"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="23"/>
       <c r="B72" s="25"/>
       <c r="C72" s="13"/>
       <c r="D72" s="15"/>
       <c r="E72" s="14"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="23"/>
       <c r="B73" s="25"/>
       <c r="C73" s="13"/>
       <c r="D73" s="15"/>
       <c r="E73" s="14"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="23"/>
       <c r="B74" s="25"/>
       <c r="C74" s="13"/>
       <c r="D74" s="15"/>
       <c r="E74" s="14"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="23"/>
       <c r="B75" s="25"/>
       <c r="C75" s="13"/>
       <c r="D75" s="15"/>
       <c r="E75" s="14"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="23"/>
       <c r="B76" s="25"/>
       <c r="C76" s="13"/>
       <c r="D76" s="15"/>
       <c r="E76" s="14"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="23"/>
       <c r="B77" s="25"/>
       <c r="C77" s="13"/>
       <c r="D77" s="15"/>
       <c r="E77" s="14"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="23"/>
       <c r="B78" s="25"/>
       <c r="C78" s="13"/>
       <c r="D78" s="15"/>
       <c r="E78" s="14"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="23"/>
       <c r="B79" s="25"/>
       <c r="C79" s="13"/>
       <c r="D79" s="15"/>
       <c r="E79" s="14"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="23"/>
       <c r="B80" s="25"/>
       <c r="C80" s="13"/>
       <c r="D80" s="15"/>
       <c r="E80" s="14"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="23"/>
       <c r="B81" s="25"/>
       <c r="C81" s="13"/>
       <c r="D81" s="15"/>
       <c r="E81" s="14"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="23"/>
       <c r="B82" s="25"/>
       <c r="C82" s="13"/>
       <c r="D82" s="15"/>
       <c r="E82" s="14"/>
     </row>
-    <row r="83" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="23"/>
       <c r="B83" s="25"/>
       <c r="C83" s="13"/>
       <c r="D83" s="15"/>
       <c r="E83" s="14"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="23"/>
       <c r="B84" s="25"/>
       <c r="C84" s="13"/>
       <c r="D84" s="15"/>
       <c r="E84" s="14"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="23"/>
       <c r="B85" s="25"/>
       <c r="C85" s="13"/>
       <c r="D85" s="15"/>
       <c r="E85" s="14"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="23"/>
       <c r="B86" s="25"/>
       <c r="C86" s="13"/>
       <c r="D86" s="15"/>
       <c r="E86" s="14"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="23"/>
       <c r="B87" s="25"/>
       <c r="C87" s="13"/>
       <c r="D87" s="15"/>
       <c r="E87" s="14"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="23"/>
       <c r="B88" s="25"/>
       <c r="C88" s="13"/>
       <c r="D88" s="15"/>
       <c r="E88" s="14"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="23"/>
       <c r="B89" s="25"/>
       <c r="C89" s="13"/>
       <c r="D89" s="15"/>
       <c r="E89" s="14"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="23"/>
       <c r="B90" s="25"/>
       <c r="C90" s="13"/>
       <c r="D90" s="15"/>
       <c r="E90" s="14"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="23"/>
       <c r="B91" s="25"/>
       <c r="C91" s="13"/>
       <c r="D91" s="15"/>
       <c r="E91" s="14"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="23"/>
       <c r="B92" s="25"/>
       <c r="C92" s="13"/>
       <c r="D92" s="15"/>
       <c r="E92" s="14"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="23"/>
       <c r="B93" s="25"/>
       <c r="C93" s="13"/>
       <c r="D93" s="15"/>
       <c r="E93" s="14"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="23"/>
       <c r="B94" s="25"/>
       <c r="C94" s="13"/>
       <c r="D94" s="15"/>
       <c r="E94" s="14"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="23"/>
       <c r="B95" s="25"/>
       <c r="C95" s="13"/>
       <c r="D95" s="15"/>
       <c r="E95" s="14"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="23"/>
       <c r="B96" s="25"/>
       <c r="C96" s="13"/>
       <c r="D96" s="15"/>
       <c r="E96" s="14"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="23"/>
       <c r="B97" s="25"/>
       <c r="C97" s="13"/>
       <c r="D97" s="15"/>
       <c r="E97" s="14"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="23"/>
       <c r="B98" s="25"/>
       <c r="C98" s="13"/>
       <c r="D98" s="15"/>
       <c r="E98" s="14"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="23"/>
       <c r="B99" s="25"/>
       <c r="C99" s="13"/>
       <c r="D99" s="15"/>
       <c r="E99" s="14"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="23"/>
       <c r="B100" s="25"/>
       <c r="C100" s="13"/>
       <c r="D100" s="15"/>
       <c r="E100" s="14"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="23"/>
       <c r="B101" s="25"/>
       <c r="C101" s="13"/>
       <c r="D101" s="15"/>
       <c r="E101" s="14"/>
     </row>
-    <row r="102" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="23"/>
       <c r="B102" s="25"/>
       <c r="C102" s="13"/>
       <c r="D102" s="15"/>
       <c r="E102" s="14"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="23"/>
       <c r="B103" s="25"/>
       <c r="C103" s="13"/>
       <c r="D103" s="15"/>
       <c r="E103" s="14"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="23"/>
       <c r="B104" s="25"/>
       <c r="C104" s="13"/>
       <c r="D104" s="15"/>
       <c r="E104" s="14"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="23"/>
       <c r="B105" s="25"/>
       <c r="C105" s="13"/>
       <c r="D105" s="15"/>
       <c r="E105" s="14"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="23"/>
       <c r="B106" s="25"/>
       <c r="C106" s="13"/>
       <c r="D106" s="15"/>
       <c r="E106" s="14"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="23"/>
       <c r="B107" s="25"/>
       <c r="C107" s="13"/>
       <c r="D107" s="15"/>
       <c r="E107" s="14"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="23"/>
       <c r="B108" s="25"/>
       <c r="C108" s="13"/>
       <c r="D108" s="15"/>
       <c r="E108" s="14"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="23"/>
       <c r="B109" s="25"/>
       <c r="C109" s="13"/>
       <c r="D109" s="15"/>
       <c r="E109" s="14"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="23"/>
       <c r="B110" s="25"/>
       <c r="C110" s="13"/>
       <c r="D110" s="15"/>
       <c r="E110" s="14"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="23"/>
       <c r="B111" s="25"/>
       <c r="C111" s="13"/>
       <c r="D111" s="15"/>
       <c r="E111" s="14"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="23"/>
       <c r="B112" s="25"/>
       <c r="C112" s="13"/>
       <c r="D112" s="15"/>
       <c r="E112" s="14"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="23"/>
       <c r="B113" s="25"/>
       <c r="C113" s="13"/>
       <c r="D113" s="15"/>
       <c r="E113" s="14"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="23"/>
       <c r="B114" s="25"/>
       <c r="C114" s="13"/>
       <c r="D114" s="15"/>
       <c r="E114" s="14"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="23"/>
       <c r="B115" s="25"/>
       <c r="C115" s="13"/>
       <c r="D115" s="15"/>
       <c r="E115" s="14"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="23"/>
       <c r="B116" s="25"/>
       <c r="C116" s="13"/>
       <c r="D116" s="15"/>
       <c r="E116" s="14"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="23"/>
       <c r="B117" s="25"/>
       <c r="C117" s="13"/>
       <c r="D117" s="15"/>
       <c r="E117" s="14"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="23"/>
       <c r="B118" s="25"/>
       <c r="C118" s="13"/>
       <c r="D118" s="15"/>
       <c r="E118" s="14"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="23"/>
       <c r="B119" s="25"/>
       <c r="C119" s="13"/>
       <c r="D119" s="15"/>
       <c r="E119" s="14"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="23"/>
       <c r="B120" s="25"/>
       <c r="C120" s="13"/>
       <c r="D120" s="15"/>
       <c r="E120" s="14"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="8"/>
       <c r="E121" s="9"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="8"/>
       <c r="E122" s="9"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="8"/>
       <c r="E123" s="9"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="8"/>
       <c r="E124" s="9"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="8"/>
       <c r="B125" s="9"/>
       <c r="C125" s="8"/>
       <c r="E125" s="9"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="8"/>
       <c r="E126" s="9"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="8"/>
       <c r="E127" s="9"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="8"/>
       <c r="E128" s="9"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="8"/>
       <c r="E129" s="9"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="8"/>
       <c r="B130" s="9"/>
       <c r="C130" s="8"/>
       <c r="E130" s="9"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
       <c r="E131" s="9"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="8"/>
       <c r="B132" s="9"/>
       <c r="C132" s="8"/>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="8"/>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="8"/>
       <c r="E134" s="9"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="8"/>
       <c r="E135" s="9"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="8"/>
       <c r="E136" s="9"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="8"/>
       <c r="E137" s="9"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="10"/>
       <c r="D138" s="12"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="8"/>
       <c r="B145" s="9"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="8"/>
       <c r="B146" s="9"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="8"/>
       <c r="B147" s="9"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="8"/>
       <c r="B148" s="9"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="8"/>
       <c r="B149" s="9"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="8"/>
       <c r="B150" s="9"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="8"/>
       <c r="B151" s="9"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="8"/>
       <c r="B152" s="9"/>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="8"/>
       <c r="B153" s="9"/>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="8"/>
       <c r="B154" s="9"/>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="8"/>
       <c r="B155" s="9"/>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="8"/>
       <c r="B156" s="9"/>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="8"/>
       <c r="B157" s="9"/>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="8"/>
       <c r="B158" s="9"/>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="8"/>
       <c r="B159" s="9"/>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="8"/>
       <c r="B160" s="9"/>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="8"/>
       <c r="B161" s="9"/>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="8"/>
       <c r="B162" s="9"/>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="8"/>
       <c r="B163" s="9"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="8"/>
       <c r="B164" s="9"/>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="8"/>
       <c r="B165" s="9"/>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="8"/>
       <c r="B166" s="9"/>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="8"/>
       <c r="B167" s="9"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="8"/>
       <c r="B168" s="9"/>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="8"/>
       <c r="B169" s="9"/>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="8"/>
       <c r="B170" s="9"/>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="8"/>
       <c r="B171" s="9"/>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="8"/>
       <c r="B172" s="9"/>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="8"/>
       <c r="B173" s="9"/>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="8"/>
       <c r="B174" s="9"/>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="8"/>
       <c r="B175" s="9"/>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="8"/>
       <c r="B176" s="9"/>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="8"/>
       <c r="B177" s="9"/>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="8"/>
       <c r="B178" s="9"/>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="8"/>
       <c r="B179" s="9"/>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="8"/>
       <c r="B181" s="9"/>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="8"/>
       <c r="B182" s="9"/>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="8"/>
       <c r="B184" s="9"/>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="8"/>
       <c r="B185" s="9"/>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="8"/>
       <c r="B186" s="9"/>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="8"/>
       <c r="B187" s="9"/>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="8"/>
       <c r="B188" s="9"/>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="8"/>
       <c r="B189" s="9"/>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="8"/>
       <c r="B190" s="9"/>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="8"/>
       <c r="B192" s="9"/>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" s="8"/>
       <c r="B193" s="9"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="8"/>
       <c r="B194" s="9"/>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="8"/>
       <c r="B195" s="9"/>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="8"/>
       <c r="B196" s="9"/>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="8"/>
       <c r="B197" s="9"/>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="8"/>
       <c r="B198" s="9"/>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="8"/>
       <c r="B199" s="9"/>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="8"/>
       <c r="B200" s="9"/>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="8"/>
       <c r="B201" s="9"/>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="8"/>
       <c r="B202" s="9"/>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="8"/>
       <c r="B203" s="9"/>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="8"/>
       <c r="B204" s="9"/>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="8"/>
       <c r="B205" s="9"/>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="8"/>
       <c r="B206" s="9"/>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="8"/>
       <c r="B207" s="9"/>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="8"/>
       <c r="B208" s="9"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="8"/>
       <c r="B209" s="9"/>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="8"/>
       <c r="B210" s="9"/>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="8"/>
       <c r="B211" s="9"/>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="8"/>
       <c r="B212" s="9"/>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="8"/>
       <c r="B213" s="9"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="8"/>
       <c r="B214" s="9"/>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="8"/>
       <c r="B215" s="9"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="8"/>
       <c r="B216" s="9"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="8"/>
       <c r="B217" s="9"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="8"/>
       <c r="B218" s="9"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" s="8"/>
       <c r="B219" s="9"/>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" s="8"/>
       <c r="B220" s="9"/>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" s="8"/>
       <c r="B221" s="9"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" s="8"/>
       <c r="B222" s="9"/>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" s="8"/>
       <c r="B223" s="9"/>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" s="8"/>
       <c r="B224" s="9"/>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" s="8"/>
       <c r="B225" s="9"/>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" s="8"/>
       <c r="B226" s="9"/>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="8"/>
       <c r="B227" s="9"/>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" s="8"/>
       <c r="B228" s="9"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" s="8"/>
       <c r="B229" s="9"/>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="8"/>
       <c r="B230" s="9"/>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" s="8"/>
       <c r="B231" s="9"/>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" s="8"/>
       <c r="B232" s="9"/>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="8"/>
       <c r="B233" s="9"/>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" s="8"/>
       <c r="B234" s="9"/>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="8"/>
       <c r="B235" s="9"/>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" s="8"/>
       <c r="B236" s="9"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" s="8"/>
       <c r="B237" s="9"/>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" s="8"/>
       <c r="B238" s="9"/>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="8"/>
       <c r="B239" s="9"/>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="8"/>
       <c r="B240" s="9"/>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="8"/>
       <c r="B241" s="9"/>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="8"/>
       <c r="B242" s="9"/>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="8"/>
       <c r="B243" s="9"/>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="8"/>
       <c r="B244" s="9"/>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="8"/>
       <c r="B245" s="9"/>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="8"/>
       <c r="B246" s="9"/>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="8"/>
       <c r="B247" s="9"/>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="8"/>
       <c r="B248" s="9"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="8"/>
       <c r="B249" s="9"/>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="8"/>
       <c r="B251" s="9"/>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="8"/>
       <c r="B252" s="9"/>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="8"/>
       <c r="B253" s="9"/>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="8"/>
       <c r="B254" s="9"/>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="8"/>
       <c r="B255" s="9"/>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="8"/>
       <c r="B256" s="9"/>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" s="8"/>
       <c r="B257" s="9"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" s="8"/>
       <c r="B258" s="9"/>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="8"/>
       <c r="B259" s="9"/>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" s="8"/>
       <c r="B260" s="9"/>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="8"/>
       <c r="B261" s="9"/>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" s="8"/>
       <c r="B262" s="9"/>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" s="8"/>
       <c r="B263" s="9"/>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" s="8"/>
       <c r="B264" s="9"/>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" s="8"/>
       <c r="B265" s="9"/>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="8"/>
       <c r="B266" s="9"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="8"/>
       <c r="B267" s="9"/>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="8"/>
       <c r="B268" s="9"/>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="8"/>
       <c r="B269" s="9"/>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="8"/>
       <c r="B270" s="9"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="8"/>
       <c r="B271" s="9"/>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="8"/>
       <c r="B272" s="9"/>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="8"/>
       <c r="B273" s="9"/>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="8"/>
       <c r="B274" s="9"/>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="8"/>
       <c r="B275" s="9"/>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="8"/>
       <c r="B276" s="9"/>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="8"/>
       <c r="B277" s="9"/>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="8"/>
       <c r="B278" s="9"/>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="8"/>
       <c r="B279" s="9"/>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="8"/>
       <c r="B280" s="9"/>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="8"/>
       <c r="B281" s="9"/>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="8"/>
       <c r="B282" s="9"/>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="8"/>
       <c r="B283" s="9"/>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="8"/>
       <c r="B284" s="9"/>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="8"/>
       <c r="B285" s="9"/>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="8"/>
       <c r="B286" s="9"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="8"/>
       <c r="B287" s="9"/>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="8"/>
       <c r="B288" s="9"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="8"/>
       <c r="B289" s="9"/>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="8"/>
       <c r="B290" s="9"/>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="8"/>
       <c r="B291" s="9"/>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="8"/>
       <c r="B292" s="9"/>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="8"/>
       <c r="B293" s="9"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="8"/>
       <c r="B294" s="9"/>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="8"/>
       <c r="B295" s="9"/>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="8"/>
       <c r="B296" s="9"/>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="8"/>
       <c r="B298" s="9"/>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="8"/>
       <c r="B299" s="9"/>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" s="8"/>
       <c r="B300" s="9"/>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" s="8"/>
       <c r="B301" s="9"/>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" s="8"/>
       <c r="B302" s="9"/>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" s="8"/>
       <c r="B303" s="9"/>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" s="8"/>
       <c r="B304" s="9"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="8"/>
       <c r="B305" s="9"/>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" s="8"/>
       <c r="B306" s="9"/>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="8"/>
       <c r="B307" s="9"/>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" s="8"/>
       <c r="B308" s="9"/>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" s="8"/>
       <c r="B310" s="9"/>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" s="8"/>
       <c r="B311" s="9"/>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" s="8"/>
       <c r="B312" s="9"/>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" s="8"/>
       <c r="B313" s="9"/>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" s="8"/>
       <c r="B314" s="9"/>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" s="8"/>
       <c r="B315" s="9"/>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" s="8"/>
       <c r="B316" s="9"/>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" s="8"/>
       <c r="B317" s="9"/>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" s="8"/>
       <c r="B318" s="9"/>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" s="8"/>
       <c r="B319" s="9"/>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" s="8"/>
       <c r="B320" s="9"/>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" s="8"/>
       <c r="B321" s="9"/>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" s="8"/>
       <c r="B322" s="9"/>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" s="8"/>
       <c r="B323" s="9"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" s="8"/>
       <c r="B324" s="9"/>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" s="8"/>
       <c r="B325" s="9"/>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" s="8"/>
       <c r="B326" s="9"/>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" s="8"/>
       <c r="B327" s="9"/>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" s="8"/>
       <c r="B328" s="9"/>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" s="8"/>
       <c r="B329" s="9"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" s="8"/>
       <c r="B330" s="9"/>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" s="8"/>
       <c r="B331" s="9"/>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" s="8"/>
       <c r="B332" s="9"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" s="8"/>
       <c r="B333" s="9"/>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" s="8"/>
       <c r="B334" s="9"/>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" s="8"/>
       <c r="B335" s="9"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" s="8"/>
       <c r="B336" s="9"/>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" s="8"/>
       <c r="B337" s="9"/>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" s="8"/>
       <c r="B338" s="9"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" s="8"/>
       <c r="B339" s="9"/>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" s="8"/>
       <c r="B340" s="9"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" s="8"/>
       <c r="B341" s="9"/>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" s="8"/>
       <c r="B342" s="9"/>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" s="8"/>
       <c r="B343" s="9"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" s="8"/>
       <c r="B344" s="9"/>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" s="8"/>
       <c r="B345" s="9"/>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" s="8"/>
       <c r="B346" s="9"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" s="8"/>
       <c r="B347" s="9"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" s="8"/>
       <c r="B348" s="9"/>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" s="8"/>
       <c r="B349" s="9"/>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" s="8"/>
       <c r="B350" s="9"/>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" s="8"/>
       <c r="B351" s="9"/>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" s="8"/>
       <c r="B352" s="9"/>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" s="8"/>
       <c r="B353" s="9"/>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" s="8"/>
       <c r="B354" s="9"/>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" s="8"/>
       <c r="B355" s="9"/>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" s="8"/>
       <c r="B356" s="9"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" s="8"/>
       <c r="B357" s="9"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" s="8"/>
       <c r="B358" s="9"/>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" s="8"/>
       <c r="B359" s="9"/>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" s="8"/>
       <c r="B360" s="9"/>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" s="8"/>
       <c r="B361" s="9"/>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" s="8"/>
       <c r="B362" s="9"/>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" s="8"/>
       <c r="B363" s="9"/>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" s="8"/>
       <c r="B364" s="9"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" s="8"/>
       <c r="B365" s="9"/>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" s="8"/>
       <c r="B366" s="9"/>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" s="8"/>
       <c r="B367" s="9"/>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" s="8"/>
       <c r="B370" s="9"/>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" s="8"/>
       <c r="B371" s="9"/>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" s="8"/>
       <c r="B372" s="9"/>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" s="8"/>
       <c r="B373" s="9"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" s="8"/>
       <c r="B374" s="9"/>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" s="8"/>
       <c r="B375" s="9"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" s="8"/>
       <c r="B376" s="9"/>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" s="8"/>
       <c r="B377" s="9"/>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" s="8"/>
       <c r="B378" s="9"/>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" s="8"/>
       <c r="B379" s="9"/>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" s="8"/>
       <c r="B380" s="9"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" s="8"/>
       <c r="B381" s="9"/>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" s="8"/>
       <c r="B382" s="9"/>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" s="8"/>
       <c r="B383" s="9"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" s="8"/>
       <c r="B384" s="9"/>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" s="8"/>
       <c r="B385" s="9"/>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" s="8"/>
       <c r="B386" s="9"/>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" s="8"/>
       <c r="B387" s="9"/>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" s="8"/>
       <c r="B388" s="9"/>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" s="8"/>
       <c r="B389" s="9"/>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" s="8"/>
       <c r="B390" s="9"/>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" s="8"/>
       <c r="B391" s="9"/>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" s="8"/>
       <c r="B392" s="9"/>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" s="8"/>
       <c r="B393" s="9"/>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" s="8"/>
       <c r="B394" s="9"/>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" s="8"/>
       <c r="B395" s="9"/>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" s="8"/>
       <c r="B396" s="9"/>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" s="8"/>
       <c r="B397" s="9"/>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" s="8"/>
       <c r="B398" s="9"/>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" s="8"/>
       <c r="B399" s="9"/>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" s="8"/>
       <c r="B400" s="9"/>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" s="8"/>
       <c r="B401" s="9"/>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" s="8"/>
       <c r="B402" s="9"/>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" s="8"/>
       <c r="B403" s="9"/>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" s="8"/>
       <c r="B404" s="9"/>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" s="8"/>
       <c r="B405" s="9"/>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" s="8"/>
       <c r="B406" s="9"/>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" s="8"/>
       <c r="B407" s="9"/>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" s="8"/>
       <c r="B408" s="9"/>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" s="8"/>
       <c r="B409" s="9"/>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" s="8"/>
       <c r="B410" s="9"/>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" s="8"/>
       <c r="B411" s="9"/>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" s="8"/>
       <c r="B412" s="9"/>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" s="8"/>
       <c r="B413" s="9"/>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" s="8"/>
       <c r="B414" s="9"/>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" s="8"/>
       <c r="B415" s="9"/>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" s="8"/>
       <c r="B416" s="9"/>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" s="8"/>
       <c r="B417" s="9"/>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" s="8"/>
       <c r="B418" s="9"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" s="8"/>
       <c r="B419" s="9"/>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" s="8"/>
       <c r="B420" s="9"/>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" s="8"/>
       <c r="B421" s="9"/>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" s="8"/>
       <c r="B422" s="9"/>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" s="8"/>
       <c r="B423" s="9"/>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" s="8"/>
       <c r="B424" s="9"/>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" s="8"/>
       <c r="B425" s="9"/>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" s="8"/>
       <c r="B426" s="9"/>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" s="8"/>
       <c r="B427" s="9"/>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" s="8"/>
       <c r="B428" s="9"/>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" s="8"/>
       <c r="B429" s="9"/>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" s="8"/>
       <c r="B430" s="9"/>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" s="8"/>
       <c r="B431" s="9"/>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" s="8"/>
       <c r="B432" s="9"/>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" s="8"/>
       <c r="B433" s="9"/>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" s="8"/>
       <c r="B434" s="9"/>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" s="8"/>
       <c r="B435" s="9"/>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" s="8"/>
       <c r="B436" s="9"/>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" s="8"/>
       <c r="B437" s="9"/>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" s="8"/>
       <c r="B438" s="9"/>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" s="8"/>
       <c r="B439" s="9"/>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" s="8"/>
       <c r="B440" s="9"/>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" s="8"/>
       <c r="B441" s="9"/>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" s="8"/>
       <c r="B442" s="9"/>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" s="8"/>
       <c r="B443" s="9"/>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" s="8"/>
       <c r="B444" s="9"/>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" s="8"/>
       <c r="B445" s="9"/>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" s="8"/>
       <c r="B446" s="9"/>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" s="8"/>
       <c r="B447" s="9"/>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" s="8"/>
       <c r="B448" s="9"/>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" s="8"/>
       <c r="B449" s="9"/>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" s="8"/>
       <c r="B450" s="9"/>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" s="8"/>
       <c r="B451" s="9"/>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" s="8"/>
       <c r="B452" s="9"/>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" s="8"/>
       <c r="B453" s="9"/>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" s="8"/>
       <c r="B454" s="9"/>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" s="8"/>
       <c r="B455" s="9"/>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" s="8"/>
       <c r="B456" s="9"/>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" s="8"/>
       <c r="B457" s="9"/>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" s="8"/>
       <c r="B458" s="9"/>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" s="8"/>
       <c r="B459" s="9"/>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" s="8"/>
       <c r="B460" s="9"/>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" s="8"/>
       <c r="B461" s="9"/>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" s="8"/>
       <c r="B462" s="9"/>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" s="8"/>
       <c r="B463" s="9"/>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" s="8"/>
       <c r="B464" s="9"/>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" s="8"/>
       <c r="B465" s="9"/>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" s="8"/>
       <c r="B466" s="9"/>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" s="8"/>
       <c r="B467" s="9"/>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" s="8"/>
       <c r="B468" s="9"/>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" s="8"/>
       <c r="B469" s="9"/>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" s="8"/>
       <c r="B470" s="9"/>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" s="8"/>
       <c r="B471" s="9"/>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" s="8"/>
       <c r="B472" s="9"/>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" s="8"/>
       <c r="B473" s="9"/>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" s="8"/>
       <c r="B474" s="9"/>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" s="8"/>
       <c r="B475" s="9"/>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" s="8"/>
       <c r="B476" s="9"/>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" s="8"/>
       <c r="B477" s="9"/>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" s="8"/>
       <c r="B478" s="9"/>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" s="8"/>
       <c r="B479" s="9"/>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" s="8"/>
       <c r="B480" s="9"/>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" s="8"/>
       <c r="B481" s="9"/>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" s="8"/>
       <c r="B482" s="9"/>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" s="8"/>
       <c r="B483" s="9"/>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" s="8"/>
       <c r="B484" s="9"/>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" s="8"/>
       <c r="B485" s="9"/>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" s="8"/>
       <c r="B486" s="9"/>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" s="8"/>
       <c r="B487" s="9"/>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" s="8"/>
       <c r="B488" s="9"/>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" s="8"/>
       <c r="B489" s="9"/>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" s="8"/>
       <c r="B490" s="9"/>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" s="8"/>
       <c r="B491" s="9"/>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" s="8"/>
       <c r="B492" s="9"/>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" s="8"/>
       <c r="B493" s="9"/>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" s="8"/>
       <c r="B494" s="9"/>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" s="8"/>
       <c r="B495" s="9"/>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" s="8"/>
       <c r="B496" s="9"/>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" s="8"/>
       <c r="B497" s="9"/>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" s="8"/>
       <c r="B498" s="9"/>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" s="8"/>
       <c r="B499" s="9"/>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" s="8"/>
       <c r="B500" s="9"/>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" s="8"/>
       <c r="B501" s="9"/>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" s="8"/>
       <c r="B502" s="9"/>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" s="8"/>
       <c r="B503" s="9"/>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" s="8"/>
       <c r="B504" s="9"/>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" s="8"/>
       <c r="B505" s="9"/>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" s="8"/>
       <c r="B506" s="9"/>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" s="8"/>
       <c r="B507" s="9"/>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" s="8"/>
       <c r="B508" s="9"/>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" s="8"/>
       <c r="B509" s="9"/>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" s="8"/>
       <c r="B510" s="9"/>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" s="8"/>
       <c r="B511" s="9"/>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" s="8"/>
       <c r="B512" s="9"/>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" s="8"/>
       <c r="B513" s="9"/>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" s="8"/>
       <c r="B514" s="9"/>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" s="8"/>
       <c r="B515" s="9"/>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" s="8"/>
       <c r="B516" s="9"/>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" s="8"/>
       <c r="B517" s="9"/>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" s="8"/>
       <c r="B518" s="9"/>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" s="8"/>
       <c r="B519" s="9"/>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" s="8"/>
       <c r="B520" s="9"/>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" s="8"/>
       <c r="B521" s="9"/>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" s="8"/>
       <c r="B522" s="9"/>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" s="8"/>
       <c r="B523" s="9"/>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" s="8"/>
       <c r="B524" s="9"/>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" s="8"/>
       <c r="B525" s="9"/>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" s="8"/>
       <c r="B526" s="9"/>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" s="8"/>
       <c r="B527" s="9"/>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" s="8"/>
       <c r="B528" s="9"/>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" s="8"/>
       <c r="B529" s="9"/>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" s="8"/>
       <c r="B530" s="9"/>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" s="8"/>
       <c r="B531" s="9"/>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" s="8"/>
       <c r="B532" s="9"/>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" s="8"/>
       <c r="B533" s="9"/>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" s="8"/>
       <c r="B534" s="9"/>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" s="8"/>
       <c r="B535" s="9"/>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" s="8"/>
       <c r="B536" s="9"/>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" s="8"/>
       <c r="B537" s="9"/>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" s="8"/>
       <c r="B538" s="9"/>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" s="8"/>
       <c r="B539" s="9"/>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" s="8"/>
       <c r="B540" s="9"/>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" s="8"/>
       <c r="B541" s="9"/>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" s="8"/>
       <c r="B542" s="9"/>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" s="8"/>
       <c r="B543" s="9"/>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" s="8"/>
       <c r="B544" s="9"/>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" s="8"/>
       <c r="B545" s="9"/>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" s="8"/>
       <c r="B546" s="9"/>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" s="8"/>
       <c r="B547" s="9"/>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" s="8"/>
       <c r="B548" s="9"/>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" s="8"/>
       <c r="B549" s="9"/>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" s="8"/>
       <c r="B550" s="9"/>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" s="8"/>
       <c r="B551" s="9"/>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" s="8"/>
       <c r="B552" s="9"/>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" s="8"/>
       <c r="B553" s="9"/>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" s="8"/>
       <c r="B554" s="9"/>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" s="8"/>
       <c r="B555" s="9"/>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" s="8"/>
       <c r="B556" s="9"/>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" s="8"/>
       <c r="B557" s="9"/>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" s="8"/>
       <c r="B558" s="9"/>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" s="8"/>
       <c r="B559" s="9"/>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" s="8"/>
       <c r="B560" s="9"/>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" s="8"/>
       <c r="B561" s="9"/>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" s="8"/>
       <c r="B562" s="9"/>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" s="8"/>
       <c r="B563" s="9"/>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" s="8"/>
       <c r="B564" s="9"/>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" s="8"/>
       <c r="B565" s="9"/>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" s="8"/>
       <c r="B566" s="9"/>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" s="8"/>
       <c r="B567" s="9"/>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" s="8"/>
       <c r="B568" s="9"/>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" s="8"/>
       <c r="B569" s="9"/>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" s="8"/>
       <c r="B570" s="9"/>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" s="8"/>
       <c r="B571" s="9"/>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" s="8"/>
       <c r="B572" s="9"/>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" s="8"/>
       <c r="B573" s="9"/>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" s="8"/>
       <c r="B574" s="9"/>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" s="8"/>
       <c r="B575" s="9"/>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" s="8"/>
       <c r="B576" s="9"/>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" s="8"/>
       <c r="B577" s="9"/>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" s="8"/>
       <c r="B578" s="9"/>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" s="8"/>
       <c r="B579" s="9"/>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" s="8"/>
       <c r="B580" s="9"/>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" s="8"/>
       <c r="B581" s="9"/>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" s="8"/>
       <c r="B582" s="9"/>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" s="8"/>
       <c r="B583" s="9"/>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" s="8"/>
       <c r="B584" s="9"/>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" s="8"/>
       <c r="B585" s="9"/>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" s="8"/>
       <c r="B586" s="9"/>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" s="8"/>
       <c r="B587" s="9"/>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" s="8"/>
       <c r="B588" s="9"/>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" s="8"/>
       <c r="B589" s="9"/>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" s="8"/>
       <c r="B590" s="9"/>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" s="8"/>
       <c r="B591" s="9"/>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" s="8"/>
       <c r="B592" s="9"/>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="8"/>
       <c r="B593" s="9"/>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="8"/>
       <c r="B594" s="9"/>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="8"/>
       <c r="B595" s="9"/>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="8"/>
       <c r="B596" s="9"/>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="8"/>
       <c r="B597" s="9"/>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="8"/>
       <c r="B598" s="9"/>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="8"/>
       <c r="B599" s="9"/>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="8"/>
       <c r="B600" s="9"/>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="8"/>
       <c r="B601" s="9"/>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" s="8"/>
       <c r="B602" s="9"/>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" s="8"/>
       <c r="B603" s="9"/>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" s="8"/>
       <c r="B604" s="9"/>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" s="8"/>
       <c r="B605" s="9"/>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" s="8"/>
       <c r="B606" s="9"/>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" s="8"/>
       <c r="B607" s="9"/>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" s="8"/>
       <c r="B608" s="9"/>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" s="8"/>
       <c r="B609" s="9"/>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" s="8"/>
       <c r="B610" s="9"/>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" s="8"/>
       <c r="B611" s="9"/>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" s="8"/>
       <c r="B612" s="9"/>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" s="8"/>
       <c r="B613" s="9"/>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" s="8"/>
       <c r="B614" s="9"/>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" s="8"/>
       <c r="B615" s="9"/>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" s="8"/>
       <c r="B616" s="9"/>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" s="8"/>
       <c r="B617" s="9"/>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" s="8"/>
       <c r="B618" s="9"/>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" s="8"/>
       <c r="B619" s="9"/>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" s="8"/>
       <c r="B620" s="9"/>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" s="8"/>
       <c r="B621" s="9"/>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" s="8"/>
       <c r="B622" s="9"/>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" s="8"/>
       <c r="B623" s="9"/>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" s="8"/>
       <c r="B624" s="9"/>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" s="8"/>
       <c r="B625" s="9"/>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" s="8"/>
       <c r="B626" s="9"/>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" s="8"/>
       <c r="B627" s="9"/>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" s="8"/>
       <c r="B628" s="9"/>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" s="8"/>
       <c r="B629" s="9"/>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" s="8"/>
       <c r="B630" s="9"/>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" s="8"/>
       <c r="B631" s="9"/>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" s="8"/>
       <c r="B632" s="9"/>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" s="8"/>
       <c r="B633" s="9"/>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" s="8"/>
       <c r="B634" s="9"/>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" s="8"/>
       <c r="B635" s="9"/>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" s="8"/>
       <c r="B636" s="9"/>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" s="8"/>
       <c r="B637" s="9"/>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" s="8"/>
       <c r="B638" s="9"/>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" s="8"/>
       <c r="B639" s="9"/>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" s="8"/>
       <c r="B640" s="9"/>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" s="8"/>
       <c r="B641" s="9"/>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" s="8"/>
       <c r="B642" s="9"/>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" s="8"/>
       <c r="B643" s="9"/>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" s="8"/>
       <c r="B644" s="9"/>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" s="8"/>
       <c r="B645" s="9"/>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" s="8"/>
       <c r="B646" s="9"/>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" s="8"/>
       <c r="B647" s="9"/>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" s="8"/>
       <c r="B648" s="9"/>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" s="8"/>
       <c r="B649" s="9"/>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" s="8"/>
       <c r="B650" s="9"/>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" s="8"/>
       <c r="B651" s="9"/>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" s="8"/>
       <c r="B652" s="9"/>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" s="8"/>
       <c r="B653" s="9"/>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" s="8"/>
       <c r="B654" s="9"/>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" s="8"/>
       <c r="B655" s="9"/>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" s="8"/>
       <c r="B656" s="9"/>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" s="8"/>
       <c r="B657" s="9"/>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" s="8"/>
       <c r="B658" s="9"/>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" s="8"/>
       <c r="B659" s="9"/>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" s="8"/>
       <c r="B660" s="9"/>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" s="8"/>
       <c r="B661" s="9"/>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" s="8"/>
       <c r="B662" s="9"/>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" s="8"/>
       <c r="B663" s="9"/>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" s="8"/>
       <c r="B664" s="9"/>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" s="8"/>
       <c r="B665" s="9"/>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" s="8"/>
       <c r="B666" s="9"/>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" s="8"/>
       <c r="B667" s="9"/>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" s="8"/>
       <c r="B668" s="9"/>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" s="8"/>
       <c r="B669" s="9"/>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" s="8"/>
       <c r="B670" s="9"/>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" s="8"/>
       <c r="B671" s="9"/>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" s="8"/>
       <c r="B672" s="9"/>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" s="8"/>
       <c r="B673" s="9"/>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" s="8"/>
       <c r="B674" s="9"/>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" s="8"/>
       <c r="B675" s="9"/>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" s="8"/>
       <c r="B676" s="9"/>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" s="8"/>
       <c r="B677" s="9"/>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" s="8"/>
       <c r="B678" s="9"/>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" s="8"/>
       <c r="B679" s="9"/>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" s="8"/>
       <c r="B680" s="9"/>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" s="8"/>
       <c r="B681" s="9"/>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" s="8"/>
       <c r="B682" s="9"/>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" s="8"/>
       <c r="B683" s="9"/>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" s="8"/>
       <c r="B684" s="9"/>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" s="8"/>
       <c r="B685" s="9"/>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" s="8"/>
       <c r="B686" s="9"/>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" s="8"/>
       <c r="B687" s="9"/>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" s="8"/>
       <c r="B688" s="9"/>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" s="8"/>
       <c r="B689" s="9"/>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" s="8"/>
       <c r="B690" s="9"/>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" s="8"/>
       <c r="B691" s="9"/>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" s="8"/>
       <c r="B692" s="9"/>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" s="8"/>
       <c r="B693" s="9"/>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" s="8"/>
       <c r="B694" s="9"/>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" s="8"/>
       <c r="B695" s="9"/>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" s="8"/>
       <c r="B696" s="9"/>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" s="8"/>
       <c r="B697" s="9"/>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" s="8"/>
       <c r="B698" s="9"/>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" s="8"/>
       <c r="B699" s="9"/>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" s="8"/>
       <c r="B700" s="9"/>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" s="8"/>
       <c r="B701" s="9"/>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" s="8"/>
       <c r="B702" s="9"/>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" s="8"/>
       <c r="B703" s="9"/>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" s="8"/>
       <c r="B704" s="9"/>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" s="8"/>
       <c r="B705" s="9"/>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" s="8"/>
       <c r="B706" s="9"/>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" s="8"/>
       <c r="B707" s="9"/>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" s="8"/>
       <c r="B708" s="9"/>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" s="8"/>
       <c r="B709" s="9"/>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" s="8"/>
       <c r="B710" s="9"/>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" s="8"/>
       <c r="B711" s="9"/>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" s="8"/>
       <c r="B712" s="9"/>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" s="8"/>
       <c r="B713" s="9"/>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" s="8"/>
       <c r="B714" s="9"/>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" s="8"/>
       <c r="B715" s="9"/>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" s="8"/>
       <c r="B716" s="9"/>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" s="8"/>
       <c r="B717" s="9"/>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" s="8"/>
       <c r="B718" s="9"/>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" s="8"/>
       <c r="B719" s="9"/>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" s="8"/>
       <c r="B720" s="9"/>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" s="8"/>
       <c r="B721" s="9"/>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" s="8"/>
       <c r="B722" s="9"/>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" s="8"/>
       <c r="B723" s="9"/>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" s="8"/>
       <c r="B724" s="9"/>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" s="8"/>
       <c r="B725" s="9"/>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" s="8"/>
       <c r="B726" s="9"/>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" s="8"/>
       <c r="B727" s="9"/>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" s="8"/>
       <c r="B728" s="9"/>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" s="8"/>
       <c r="B729" s="9"/>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" s="8"/>
       <c r="B730" s="9"/>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" s="8"/>
       <c r="B731" s="9"/>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" s="8"/>
       <c r="B732" s="9"/>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" s="8"/>
       <c r="B733" s="9"/>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" s="8"/>
       <c r="B734" s="9"/>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" s="8"/>
       <c r="B735" s="9"/>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" s="8"/>
       <c r="B736" s="9"/>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" s="8"/>
       <c r="B737" s="9"/>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" s="8"/>
       <c r="B738" s="9"/>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" s="8"/>
       <c r="B739" s="9"/>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" s="8"/>
       <c r="B740" s="9"/>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" s="8"/>
       <c r="B741" s="9"/>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" s="8"/>
       <c r="B742" s="9"/>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" s="8"/>
       <c r="B743" s="9"/>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" s="8"/>
       <c r="B744" s="9"/>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" s="8"/>
       <c r="B745" s="9"/>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" s="8"/>
       <c r="B746" s="9"/>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" s="8"/>
       <c r="B747" s="9"/>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" s="8"/>
       <c r="B748" s="9"/>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" s="8"/>
       <c r="B749" s="9"/>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" s="8"/>
       <c r="B750" s="9"/>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" s="8"/>
       <c r="B751" s="9"/>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" s="8"/>
       <c r="B752" s="9"/>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" s="8"/>
       <c r="B753" s="9"/>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" s="8"/>
       <c r="B754" s="9"/>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" s="8"/>
       <c r="B755" s="9"/>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" s="8"/>
       <c r="B756" s="9"/>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" s="8"/>
       <c r="B757" s="9"/>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" s="8"/>
       <c r="B758" s="9"/>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" s="8"/>
       <c r="B759" s="9"/>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" s="8"/>
       <c r="B760" s="9"/>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" s="8"/>
       <c r="B761" s="9"/>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A762" s="8"/>
       <c r="B762" s="9"/>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A763" s="8"/>
       <c r="B763" s="9"/>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A764" s="8"/>
       <c r="B764" s="9"/>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A765" s="8"/>
       <c r="B765" s="9"/>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A766" s="8"/>
       <c r="B766" s="9"/>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A767" s="8"/>
       <c r="B767" s="9"/>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A768" s="8"/>
       <c r="B768" s="9"/>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A769" s="8"/>
       <c r="B769" s="9"/>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A770" s="8"/>
       <c r="B770" s="9"/>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A771" s="8"/>
       <c r="B771" s="9"/>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A772" s="8"/>
       <c r="B772" s="9"/>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A773" s="8"/>
       <c r="B773" s="9"/>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A774" s="8"/>
       <c r="B774" s="9"/>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A775" s="8"/>
       <c r="B775" s="9"/>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A776" s="8"/>
       <c r="B776" s="9"/>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A777" s="8"/>
       <c r="B777" s="9"/>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A778" s="8"/>
       <c r="B778" s="9"/>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A779" s="8"/>
       <c r="B779" s="9"/>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A780" s="8"/>
       <c r="B780" s="9"/>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A781" s="8"/>
       <c r="B781" s="9"/>
     </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A782" s="8"/>
       <c r="B782" s="9"/>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A783" s="8"/>
       <c r="B783" s="9"/>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A784" s="8"/>
       <c r="B784" s="9"/>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A785" s="8"/>
       <c r="B785" s="9"/>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A786" s="8"/>
       <c r="B786" s="9"/>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A787" s="8"/>
       <c r="B787" s="9"/>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A788" s="8"/>
       <c r="B788" s="9"/>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A789" s="8"/>
       <c r="B789" s="9"/>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A790" s="8"/>
       <c r="B790" s="9"/>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A791" s="8"/>
       <c r="B791" s="9"/>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A792" s="8"/>
       <c r="B792" s="9"/>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A793" s="8"/>
       <c r="B793" s="9"/>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A794" s="8"/>
       <c r="B794" s="9"/>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A795" s="8"/>
       <c r="B795" s="9"/>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A796" s="8"/>
       <c r="B796" s="9"/>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A797" s="8"/>
       <c r="B797" s="9"/>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A798" s="8"/>
       <c r="B798" s="9"/>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A799" s="8"/>
       <c r="B799" s="9"/>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A800" s="8"/>
       <c r="B800" s="9"/>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A801" s="8"/>
       <c r="B801" s="9"/>
     </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A802" s="8"/>
       <c r="B802" s="9"/>
     </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A803" s="8"/>
       <c r="B803" s="9"/>
     </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A804" s="8"/>
       <c r="B804" s="9"/>
     </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A805" s="8"/>
       <c r="B805" s="9"/>
     </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A806" s="8"/>
       <c r="B806" s="9"/>
     </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A807" s="8"/>
       <c r="B807" s="9"/>
     </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A808" s="8"/>
       <c r="B808" s="9"/>
     </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A809" s="8"/>
       <c r="B809" s="9"/>
     </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A810" s="8"/>
       <c r="B810" s="9"/>
     </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A811" s="8"/>
       <c r="B811" s="9"/>
     </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A812" s="8"/>
       <c r="B812" s="9"/>
     </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A813" s="8"/>
       <c r="B813" s="9"/>
     </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A814" s="8"/>
       <c r="B814" s="9"/>
     </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A815" s="8"/>
       <c r="B815" s="9"/>
     </row>
-    <row r="816" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A816" s="8"/>
       <c r="B816" s="9"/>
     </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A817" s="8"/>
       <c r="B817" s="9"/>
     </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A818" s="8"/>
       <c r="B818" s="9"/>
     </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A819" s="8"/>
       <c r="B819" s="9"/>
     </row>
-    <row r="820" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A820" s="8"/>
       <c r="B820" s="9"/>
     </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A821" s="8"/>
       <c r="B821" s="9"/>
     </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A822" s="8"/>
       <c r="B822" s="9"/>
     </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A823" s="8"/>
       <c r="B823" s="9"/>
     </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A824" s="8"/>
       <c r="B824" s="9"/>
     </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A825" s="8"/>
       <c r="B825" s="9"/>
     </row>
-    <row r="826" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A826" s="8"/>
       <c r="B826" s="9"/>
     </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A827" s="8"/>
       <c r="B827" s="9"/>
     </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A828" s="8"/>
       <c r="B828" s="9"/>
     </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A829" s="8"/>
       <c r="B829" s="9"/>
     </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A830" s="8"/>
       <c r="B830" s="9"/>
     </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A831" s="8"/>
       <c r="B831" s="9"/>
     </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A832" s="8"/>
       <c r="B832" s="9"/>
     </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A833" s="8"/>
       <c r="B833" s="9"/>
     </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A834" s="8"/>
       <c r="B834" s="9"/>
     </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A835" s="8"/>
       <c r="B835" s="9"/>
     </row>
-    <row r="836" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A836" s="8"/>
       <c r="B836" s="9"/>
     </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A837" s="8"/>
       <c r="B837" s="9"/>
     </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A838" s="8"/>
       <c r="B838" s="9"/>
     </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A839" s="8"/>
       <c r="B839" s="9"/>
     </row>
-    <row r="840" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
     </row>
-    <row r="841" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A841" s="8"/>
       <c r="B841" s="9"/>
     </row>
-    <row r="842" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A842" s="8"/>
       <c r="B842" s="9"/>
     </row>
-    <row r="843" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A843" s="8"/>
       <c r="B843" s="9"/>
     </row>
-    <row r="844" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A844" s="8"/>
       <c r="B844" s="9"/>
     </row>
-    <row r="845" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A845" s="8"/>
       <c r="B845" s="9"/>
     </row>
-    <row r="846" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A846" s="8"/>
       <c r="B846" s="9"/>
     </row>
-    <row r="847" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A847" s="8"/>
       <c r="B847" s="9"/>
     </row>
-    <row r="848" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A848" s="8"/>
       <c r="B848" s="9"/>
     </row>
-    <row r="849" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A849" s="8"/>
       <c r="B849" s="9"/>
     </row>
-    <row r="850" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A850" s="8"/>
       <c r="B850" s="9"/>
     </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A851" s="8"/>
       <c r="B851" s="9"/>
     </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A852" s="8"/>
       <c r="B852" s="9"/>
     </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A853" s="8"/>
       <c r="B853" s="9"/>
     </row>
-    <row r="854" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A854" s="8"/>
       <c r="B854" s="9"/>
     </row>
-    <row r="855" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A855" s="8"/>
       <c r="B855" s="9"/>
     </row>
-    <row r="856" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A856" s="8"/>
       <c r="B856" s="9"/>
     </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A857" s="8"/>
       <c r="B857" s="9"/>
     </row>
-    <row r="858" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A858" s="8"/>
       <c r="B858" s="9"/>
     </row>
-    <row r="859" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A859" s="8"/>
       <c r="B859" s="9"/>
     </row>
-    <row r="860" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A860" s="8"/>
       <c r="B860" s="9"/>
     </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A861" s="8"/>
       <c r="B861" s="9"/>
     </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A862" s="8"/>
       <c r="B862" s="9"/>
     </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A863" s="8"/>
       <c r="B863" s="9"/>
     </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A864" s="8"/>
       <c r="B864" s="9"/>
     </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A865" s="8"/>
       <c r="B865" s="9"/>
     </row>
-    <row r="866" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A866" s="8"/>
       <c r="B866" s="9"/>
     </row>
-    <row r="867" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A867" s="8"/>
       <c r="B867" s="9"/>
     </row>
-    <row r="868" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A868" s="8"/>
       <c r="B868" s="9"/>
     </row>
-    <row r="869" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A869" s="8"/>
       <c r="B869" s="9"/>
     </row>
-    <row r="870" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A870" s="8"/>
       <c r="B870" s="9"/>
     </row>
-    <row r="871" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A871" s="8"/>
       <c r="B871" s="9"/>
     </row>
-    <row r="872" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A872" s="8"/>
       <c r="B872" s="9"/>
     </row>
-    <row r="873" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A873" s="8"/>
       <c r="B873" s="9"/>
     </row>
-    <row r="874" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A874" s="8"/>
       <c r="B874" s="9"/>
     </row>
-    <row r="875" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A875" s="8"/>
       <c r="B875" s="9"/>
     </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A876" s="8"/>
       <c r="B876" s="9"/>
     </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A877" s="8"/>
       <c r="B877" s="9"/>
     </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A878" s="8"/>
       <c r="B878" s="9"/>
     </row>
-    <row r="879" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A879" s="8"/>
       <c r="B879" s="9"/>
     </row>
-    <row r="880" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A880" s="8"/>
       <c r="B880" s="9"/>
     </row>
-    <row r="881" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A881" s="8"/>
       <c r="B881" s="9"/>
     </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A882" s="8"/>
       <c r="B882" s="9"/>
     </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A883" s="8"/>
       <c r="B883" s="9"/>
     </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A884" s="8"/>
       <c r="B884" s="9"/>
     </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A885" s="8"/>
       <c r="B885" s="9"/>
     </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A886" s="8"/>
       <c r="B886" s="9"/>
     </row>
-    <row r="887" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A887" s="8"/>
       <c r="B887" s="9"/>
     </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A888" s="8"/>
       <c r="B888" s="9"/>
     </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A889" s="8"/>
       <c r="B889" s="9"/>
     </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A890" s="8"/>
       <c r="B890" s="9"/>
     </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A891" s="8"/>
       <c r="B891" s="9"/>
     </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A892" s="8"/>
       <c r="B892" s="9"/>
     </row>
-    <row r="893" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A893" s="8"/>
       <c r="B893" s="9"/>
     </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A894" s="8"/>
       <c r="B894" s="9"/>
     </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A895" s="8"/>
       <c r="B895" s="9"/>
     </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A896" s="8"/>
       <c r="B896" s="9"/>
     </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A897" s="8"/>
       <c r="B897" s="9"/>
     </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A898" s="8"/>
       <c r="B898" s="9"/>
     </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A899" s="8"/>
       <c r="B899" s="9"/>
     </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A900" s="8"/>
       <c r="B900" s="9"/>
     </row>
-    <row r="901" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A901" s="8"/>
       <c r="B901" s="9"/>
     </row>
-    <row r="902" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A902" s="8"/>
       <c r="B902" s="9"/>
     </row>
-    <row r="903" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A903" s="8"/>
       <c r="B903" s="9"/>
     </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A904" s="8"/>
       <c r="B904" s="9"/>
     </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A905" s="8"/>
       <c r="B905" s="9"/>
     </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A906" s="8"/>
       <c r="B906" s="9"/>
     </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A907" s="8"/>
       <c r="B907" s="9"/>
     </row>
-    <row r="908" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A908" s="8"/>
       <c r="B908" s="9"/>
     </row>
-    <row r="909" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A909" s="8"/>
       <c r="B909" s="9"/>
     </row>
-    <row r="910" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A910" s="8"/>
       <c r="B910" s="9"/>
     </row>
-    <row r="911" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A911" s="8"/>
       <c r="B911" s="9"/>
     </row>
-    <row r="912" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A912" s="8"/>
       <c r="B912" s="9"/>
     </row>
-    <row r="913" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A913" s="8"/>
       <c r="B913" s="9"/>
     </row>
-    <row r="914" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A914" s="8"/>
       <c r="B914" s="9"/>
     </row>
-    <row r="915" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A915" s="8"/>
       <c r="B915" s="9"/>
     </row>
-    <row r="916" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A916" s="8"/>
       <c r="B916" s="9"/>
     </row>
-    <row r="917" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A917" s="8"/>
       <c r="B917" s="9"/>
     </row>
-    <row r="918" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A918" s="8"/>
       <c r="B918" s="9"/>
     </row>
-    <row r="919" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A919" s="8"/>
       <c r="B919" s="9"/>
     </row>
-    <row r="920" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A920" s="8"/>
       <c r="B920" s="9"/>
     </row>
-    <row r="921" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A921" s="8"/>
       <c r="B921" s="9"/>
     </row>
-    <row r="922" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A922" s="8"/>
       <c r="B922" s="9"/>
     </row>
-    <row r="923" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A923" s="8"/>
       <c r="B923" s="9"/>
     </row>
-    <row r="924" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A924" s="8"/>
       <c r="B924" s="9"/>
     </row>
-    <row r="925" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A925" s="8"/>
       <c r="B925" s="9"/>
     </row>
-    <row r="926" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A926" s="8"/>
       <c r="B926" s="9"/>
     </row>
-    <row r="927" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A927" s="8"/>
       <c r="B927" s="9"/>
     </row>
-    <row r="928" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A928" s="8"/>
       <c r="B928" s="9"/>
     </row>
-    <row r="929" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A929" s="8"/>
       <c r="B929" s="9"/>
     </row>
-    <row r="930" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A930" s="8"/>
       <c r="B930" s="9"/>
     </row>
-    <row r="931" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A931" s="8"/>
       <c r="B931" s="9"/>
     </row>
-    <row r="932" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A932" s="8"/>
       <c r="B932" s="9"/>
     </row>
-    <row r="933" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A933" s="8"/>
       <c r="B933" s="9"/>
     </row>
-    <row r="934" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A934" s="8"/>
       <c r="B934" s="9"/>
     </row>
-    <row r="935" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A935" s="8"/>
       <c r="B935" s="9"/>
     </row>
-    <row r="936" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A936" s="8"/>
       <c r="B936" s="9"/>
     </row>
-    <row r="937" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A937" s="8"/>
       <c r="B937" s="9"/>
     </row>
-    <row r="938" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A938" s="8"/>
       <c r="B938" s="9"/>
     </row>
-    <row r="939" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A939" s="8"/>
       <c r="B939" s="9"/>
     </row>
-    <row r="940" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A940" s="8"/>
       <c r="B940" s="9"/>
     </row>
-    <row r="941" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A941" s="8"/>
       <c r="B941" s="9"/>
     </row>
-    <row r="942" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A942" s="8"/>
       <c r="B942" s="9"/>
     </row>
-    <row r="943" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A943" s="8"/>
       <c r="B943" s="9"/>
     </row>
-    <row r="944" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A944" s="8"/>
       <c r="B944" s="9"/>
     </row>
-    <row r="945" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A945" s="8"/>
       <c r="B945" s="9"/>
     </row>
-    <row r="946" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A946" s="8"/>
       <c r="B946" s="9"/>
     </row>
-    <row r="947" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A947" s="8"/>
       <c r="B947" s="9"/>
     </row>
-    <row r="948" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A948" s="8"/>
       <c r="B948" s="9"/>
     </row>
-    <row r="949" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A949" s="8"/>
       <c r="B949" s="9"/>
     </row>
-    <row r="950" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A950" s="8"/>
       <c r="B950" s="9"/>
     </row>
-    <row r="951" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A951" s="8"/>
       <c r="B951" s="9"/>
     </row>
-    <row r="952" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A952" s="8"/>
       <c r="B952" s="9"/>
     </row>
-    <row r="953" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A953" s="8"/>
       <c r="B953" s="9"/>
     </row>
-    <row r="954" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A954" s="8"/>
       <c r="B954" s="9"/>
     </row>
-    <row r="955" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A955" s="8"/>
       <c r="B955" s="9"/>
     </row>
-    <row r="956" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A956" s="8"/>
       <c r="B956" s="9"/>
     </row>
-    <row r="957" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A957" s="8"/>
       <c r="B957" s="9"/>
     </row>
-    <row r="958" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A958" s="8"/>
       <c r="B958" s="9"/>
     </row>
-    <row r="959" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A959" s="8"/>
       <c r="B959" s="9"/>
     </row>
-    <row r="960" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A960" s="8"/>
       <c r="B960" s="9"/>
     </row>
-    <row r="961" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A961" s="8"/>
       <c r="B961" s="9"/>
     </row>
-    <row r="962" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A962" s="8"/>
       <c r="B962" s="9"/>
     </row>
-    <row r="963" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A963" s="8"/>
       <c r="B963" s="9"/>
     </row>
-    <row r="964" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A964" s="8"/>
       <c r="B964" s="9"/>
     </row>
-    <row r="965" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A965" s="8"/>
       <c r="B965" s="9"/>
     </row>
-    <row r="966" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A966" s="8"/>
       <c r="B966" s="9"/>
     </row>
-    <row r="967" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A967" s="8"/>
       <c r="B967" s="9"/>
     </row>
-    <row r="968" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A968" s="8"/>
       <c r="B968" s="9"/>
     </row>
-    <row r="969" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A969" s="8"/>
       <c r="B969" s="9"/>
     </row>
-    <row r="970" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A970" s="8"/>
       <c r="B970" s="9"/>
     </row>
-    <row r="971" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A971" s="8"/>
       <c r="B971" s="9"/>
     </row>
-    <row r="972" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A972" s="8"/>
       <c r="B972" s="9"/>
     </row>
-    <row r="973" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A973" s="8"/>
       <c r="B973" s="9"/>
     </row>
-    <row r="974" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A974" s="8"/>
       <c r="B974" s="9"/>
     </row>
-    <row r="975" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A975" s="8"/>
       <c r="B975" s="9"/>
     </row>
-    <row r="976" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A976" s="8"/>
       <c r="B976" s="9"/>
     </row>
-    <row r="977" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A977" s="8"/>
       <c r="B977" s="9"/>
     </row>
-    <row r="978" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A978" s="8"/>
       <c r="B978" s="9"/>
     </row>
-    <row r="979" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A979" s="8"/>
       <c r="B979" s="9"/>
     </row>
-    <row r="980" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A980" s="8"/>
       <c r="B980" s="9"/>
     </row>
-    <row r="981" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A981" s="8"/>
       <c r="B981" s="9"/>
     </row>
-    <row r="982" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A982" s="8"/>
       <c r="B982" s="9"/>
     </row>
-    <row r="983" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A983" s="8"/>
       <c r="B983" s="9"/>
     </row>
-    <row r="984" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A984" s="8"/>
       <c r="B984" s="9"/>
     </row>
-    <row r="985" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A985" s="8"/>
       <c r="B985" s="9"/>
     </row>
-    <row r="986" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A986" s="8"/>
       <c r="B986" s="9"/>
     </row>
-    <row r="987" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A987" s="8"/>
       <c r="B987" s="9"/>
     </row>
-    <row r="988" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A988" s="8"/>
       <c r="B988" s="9"/>
     </row>
-    <row r="989" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A989" s="8"/>
       <c r="B989" s="9"/>
     </row>
-    <row r="990" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A990" s="8"/>
       <c r="B990" s="9"/>
     </row>
-    <row r="991" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A991" s="8"/>
       <c r="B991" s="9"/>
     </row>
-    <row r="992" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A992" s="8"/>
       <c r="B992" s="9"/>
     </row>
-    <row r="993" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A993" s="8"/>
       <c r="B993" s="9"/>
     </row>
-    <row r="994" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A994" s="8"/>
       <c r="B994" s="9"/>
     </row>
-    <row r="995" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A995" s="8"/>
       <c r="B995" s="9"/>
     </row>
-    <row r="996" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A996" s="8"/>
       <c r="B996" s="9"/>
     </row>
-    <row r="997" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A997" s="8"/>
       <c r="B997" s="9"/>
     </row>
-    <row r="998" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A998" s="8"/>
       <c r="B998" s="9"/>
     </row>
-    <row r="999" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A999" s="8"/>
       <c r="B999" s="9"/>
     </row>
-    <row r="1000" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1000" s="8"/>
       <c r="B1000" s="9"/>
     </row>
-    <row r="1001" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1001" s="8"/>
       <c r="B1001" s="9"/>
     </row>
-    <row r="1002" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1002" s="8"/>
       <c r="B1002" s="9"/>
     </row>
-    <row r="1003" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1003" s="8"/>
       <c r="B1003" s="9"/>
     </row>
-    <row r="1004" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1004" s="8"/>
       <c r="B1004" s="9"/>
     </row>
-    <row r="1005" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1005" s="8"/>
       <c r="B1005" s="9"/>
     </row>
-    <row r="1006" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1006" s="8"/>
       <c r="B1006" s="9"/>
     </row>
-    <row r="1007" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1007" s="8"/>
       <c r="B1007" s="9"/>
     </row>
-    <row r="1008" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1008" s="8"/>
       <c r="B1008" s="9"/>
     </row>
-    <row r="1009" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1009" s="8"/>
       <c r="B1009" s="9"/>
     </row>
-    <row r="1010" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1010" s="8"/>
       <c r="B1010" s="9"/>
     </row>
-    <row r="1011" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1011" s="8"/>
       <c r="B1011" s="9"/>
     </row>
-    <row r="1012" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1012" s="8"/>
       <c r="B1012" s="9"/>
     </row>
-    <row r="1013" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1013" s="8"/>
       <c r="B1013" s="9"/>
     </row>
-    <row r="1014" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1014" s="8"/>
       <c r="B1014" s="9"/>
     </row>
-    <row r="1015" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1015" s="8"/>
       <c r="B1015" s="9"/>
     </row>
-    <row r="1016" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1016" s="8"/>
       <c r="B1016" s="9"/>
     </row>
-    <row r="1017" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1017" s="8"/>
       <c r="B1017" s="9"/>
     </row>
-    <row r="1018" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1018" s="8"/>
       <c r="B1018" s="9"/>
     </row>
-    <row r="1019" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1019" s="8"/>
       <c r="B1019" s="9"/>
     </row>
-    <row r="1020" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1020" s="8"/>
       <c r="B1020" s="9"/>
     </row>
-    <row r="1021" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1021" s="8"/>
       <c r="B1021" s="9"/>
     </row>
-    <row r="1022" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1022" s="8"/>
       <c r="B1022" s="9"/>
     </row>
-    <row r="1023" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1023" s="8"/>
       <c r="B1023" s="9"/>
     </row>
-    <row r="1024" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1024" s="8"/>
       <c r="B1024" s="9"/>
     </row>
-    <row r="1025" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1025" s="8"/>
       <c r="B1025" s="9"/>
     </row>
-    <row r="1026" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1026" s="8"/>
       <c r="B1026" s="9"/>
     </row>
-    <row r="1027" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1027" s="8"/>
       <c r="B1027" s="9"/>
     </row>
-    <row r="1028" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1028" s="8"/>
       <c r="B1028" s="9"/>
     </row>
-    <row r="1029" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1029" s="8"/>
       <c r="B1029" s="9"/>
     </row>
-    <row r="1030" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1030" s="8"/>
       <c r="B1030" s="9"/>
     </row>
-    <row r="1031" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1031" s="8"/>
       <c r="B1031" s="9"/>
     </row>
-    <row r="1032" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1032" s="8"/>
       <c r="B1032" s="9"/>
     </row>
-    <row r="1033" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1033" s="8"/>
       <c r="B1033" s="9"/>
     </row>
-    <row r="1034" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1034" s="8"/>
       <c r="B1034" s="9"/>
     </row>
-    <row r="1035" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1035" s="8"/>
       <c r="B1035" s="9"/>
     </row>
-    <row r="1036" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1036" s="8"/>
       <c r="B1036" s="9"/>
     </row>
-    <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1037" s="8"/>
       <c r="B1037" s="9"/>
     </row>
-    <row r="1038" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1038" s="8"/>
       <c r="B1038" s="9"/>
     </row>
-    <row r="1039" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1039" s="8"/>
       <c r="B1039" s="9"/>
     </row>
-    <row r="1040" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1040" s="8"/>
       <c r="B1040" s="9"/>
     </row>
-    <row r="1041" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1041" s="8"/>
       <c r="B1041" s="9"/>
     </row>
-    <row r="1042" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1042" s="8"/>
       <c r="B1042" s="9"/>
     </row>
-    <row r="1043" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1043" s="8"/>
       <c r="B1043" s="9"/>
     </row>
-    <row r="1044" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1044" s="8"/>
       <c r="B1044" s="9"/>
     </row>
-    <row r="1045" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1045" s="8"/>
       <c r="B1045" s="9"/>
     </row>
-    <row r="1046" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1046" s="8"/>
       <c r="B1046" s="9"/>
     </row>
-    <row r="1047" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1047" s="8"/>
       <c r="B1047" s="9"/>
     </row>
-    <row r="1048" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1048" s="8"/>
       <c r="B1048" s="9"/>
     </row>
-    <row r="1049" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1049" s="8"/>
       <c r="B1049" s="9"/>
     </row>
-    <row r="1050" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1050" s="8"/>
       <c r="B1050" s="9"/>
     </row>
-    <row r="1051" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1051" s="8"/>
       <c r="B1051" s="9"/>
     </row>
-    <row r="1052" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1052" s="8"/>
       <c r="B1052" s="9"/>
     </row>
-    <row r="1053" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1053" s="8"/>
       <c r="B1053" s="9"/>
     </row>
-    <row r="1054" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1054" s="8"/>
       <c r="B1054" s="9"/>
     </row>
-    <row r="1055" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1055" s="8"/>
       <c r="B1055" s="9"/>
     </row>
-    <row r="1056" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1056" s="8"/>
       <c r="B1056" s="9"/>
     </row>
-    <row r="1057" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1057" s="8"/>
       <c r="B1057" s="9"/>
     </row>
-    <row r="1058" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1058" s="8"/>
       <c r="B1058" s="9"/>
     </row>
-    <row r="1059" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1059" s="8"/>
       <c r="B1059" s="9"/>
     </row>
-    <row r="1060" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1060" s="8"/>
       <c r="B1060" s="9"/>
     </row>
-    <row r="1061" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1061" s="8"/>
       <c r="B1061" s="9"/>
     </row>
-    <row r="1062" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1062" s="8"/>
       <c r="B1062" s="9"/>
     </row>
-    <row r="1063" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1063" s="8"/>
       <c r="B1063" s="9"/>
     </row>
-    <row r="1064" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1064" s="8"/>
       <c r="B1064" s="9"/>
     </row>
-    <row r="1065" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1065" s="8"/>
       <c r="B1065" s="9"/>
     </row>
-    <row r="1066" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1066" s="8"/>
       <c r="B1066" s="9"/>
     </row>
-    <row r="1067" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1067" s="8"/>
       <c r="B1067" s="9"/>
     </row>
-    <row r="1068" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1068" s="8"/>
       <c r="B1068" s="9"/>
     </row>
-    <row r="1069" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1069" s="8"/>
       <c r="B1069" s="9"/>
     </row>
-    <row r="1070" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1070" s="8"/>
       <c r="B1070" s="9"/>
     </row>
-    <row r="1071" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1071" s="8"/>
       <c r="B1071" s="9"/>
     </row>
-    <row r="1072" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1072" s="8"/>
       <c r="B1072" s="9"/>
     </row>
-    <row r="1073" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1073" s="8"/>
       <c r="B1073" s="9"/>
     </row>
-    <row r="1074" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1074" s="8"/>
       <c r="B1074" s="9"/>
     </row>
-    <row r="1075" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1075" s="8"/>
       <c r="B1075" s="9"/>
     </row>
-    <row r="1076" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1076" s="8"/>
       <c r="B1076" s="9"/>
     </row>
-    <row r="1077" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1077" s="8"/>
       <c r="B1077" s="9"/>
     </row>
-    <row r="1078" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1078" s="8"/>
       <c r="B1078" s="9"/>
     </row>
-    <row r="1079" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1079" s="8"/>
       <c r="B1079" s="9"/>
     </row>
-    <row r="1080" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1080" s="8"/>
       <c r="B1080" s="9"/>
     </row>
-    <row r="1081" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1081" s="8"/>
       <c r="B1081" s="9"/>
     </row>
-    <row r="1082" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1082" s="8"/>
       <c r="B1082" s="9"/>
     </row>
-    <row r="1083" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1083" s="8"/>
       <c r="B1083" s="9"/>
     </row>
-    <row r="1084" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1084" s="8"/>
       <c r="B1084" s="9"/>
     </row>
-    <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1085" s="8"/>
       <c r="B1085" s="9"/>
     </row>
-    <row r="1086" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1086" s="8"/>
       <c r="B1086" s="9"/>
     </row>
-    <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1087" s="8"/>
       <c r="B1087" s="9"/>
     </row>
-    <row r="1088" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1088" s="8"/>
       <c r="B1088" s="9"/>
     </row>
-    <row r="1089" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1089" s="8"/>
       <c r="B1089" s="9"/>
     </row>
-    <row r="1090" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1090" s="8"/>
       <c r="B1090" s="9"/>
     </row>
-    <row r="1091" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1091" s="8"/>
       <c r="B1091" s="9"/>
     </row>
-    <row r="1092" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1092" s="8"/>
       <c r="B1092" s="9"/>
     </row>
-    <row r="1093" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1093" s="8"/>
       <c r="B1093" s="9"/>
     </row>
-    <row r="1094" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1094" s="8"/>
       <c r="B1094" s="9"/>
     </row>
-    <row r="1095" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1095" s="8"/>
       <c r="B1095" s="9"/>
     </row>
-    <row r="1096" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1096" s="8"/>
       <c r="B1096" s="9"/>
     </row>
-    <row r="1097" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1097" s="8"/>
       <c r="B1097" s="9"/>
     </row>
-    <row r="1098" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1098" s="8"/>
       <c r="B1098" s="9"/>
     </row>
-    <row r="1099" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1099" s="8"/>
       <c r="B1099" s="9"/>
     </row>
-    <row r="1100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1100" s="8"/>
       <c r="B1100" s="9"/>
     </row>
-    <row r="1101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1101" s="8"/>
       <c r="B1101" s="9"/>
     </row>
-    <row r="1102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1102" s="8"/>
       <c r="B1102" s="9"/>
     </row>
-    <row r="1103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1103" s="8"/>
       <c r="B1103" s="9"/>
     </row>
-    <row r="1104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1104" s="8"/>
       <c r="B1104" s="9"/>
     </row>
-    <row r="1105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1105" s="8"/>
       <c r="B1105" s="9"/>
     </row>
-    <row r="1106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1106" s="8"/>
       <c r="B1106" s="9"/>
     </row>
-    <row r="1107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1107" s="8"/>
       <c r="B1107" s="9"/>
     </row>
-    <row r="1108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1108" s="8"/>
       <c r="B1108" s="9"/>
     </row>
-    <row r="1109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1109" s="8"/>
       <c r="B1109" s="9"/>
     </row>
-    <row r="1110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1110" s="8"/>
       <c r="B1110" s="9"/>
     </row>
-    <row r="1111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1111" s="8"/>
       <c r="B1111" s="9"/>
     </row>
-    <row r="1112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1112" s="8"/>
       <c r="B1112" s="9"/>
     </row>
-    <row r="1113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1113" s="8"/>
       <c r="B1113" s="9"/>
     </row>
-    <row r="1114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1114" s="8"/>
       <c r="B1114" s="9"/>
     </row>
-    <row r="1115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1115" s="8"/>
       <c r="B1115" s="9"/>
     </row>
-    <row r="1116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1116" s="8"/>
       <c r="B1116" s="9"/>
     </row>
-    <row r="1117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1117" s="8"/>
       <c r="B1117" s="9"/>
     </row>
-    <row r="1118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1118" s="8"/>
       <c r="B1118" s="9"/>
     </row>
-    <row r="1119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1119" s="8"/>
       <c r="B1119" s="9"/>
     </row>
-    <row r="1120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1120" s="8"/>
       <c r="B1120" s="9"/>
     </row>
-    <row r="1121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1121" s="8"/>
       <c r="B1121" s="9"/>
     </row>
-    <row r="1122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1122" s="8"/>
       <c r="B1122" s="9"/>
     </row>
-    <row r="1123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1123" s="8"/>
       <c r="B1123" s="9"/>
     </row>
-    <row r="1124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1124" s="8"/>
       <c r="B1124" s="9"/>
     </row>
-    <row r="1125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1125" s="8"/>
       <c r="B1125" s="9"/>
     </row>
-    <row r="1126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1126" s="8"/>
       <c r="B1126" s="9"/>
     </row>
-    <row r="1127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1127" s="8"/>
       <c r="B1127" s="9"/>
     </row>
-    <row r="1128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1128" s="8"/>
       <c r="B1128" s="9"/>
     </row>
-    <row r="1129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1129" s="8"/>
       <c r="B1129" s="9"/>
     </row>
-    <row r="1130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1130" s="8"/>
       <c r="B1130" s="9"/>
     </row>
-    <row r="1131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1131" s="8"/>
       <c r="B1131" s="9"/>
     </row>
-    <row r="1132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1132" s="8"/>
       <c r="B1132" s="9"/>
     </row>
-    <row r="1133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1133" s="8"/>
       <c r="B1133" s="9"/>
     </row>
-    <row r="1134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1134" s="8"/>
       <c r="B1134" s="9"/>
     </row>
-    <row r="1135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1135" s="8"/>
       <c r="B1135" s="9"/>
     </row>
-    <row r="1136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1136" s="8"/>
       <c r="B1136" s="9"/>
     </row>
-    <row r="1137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1137" s="8"/>
       <c r="B1137" s="9"/>
     </row>
-    <row r="1138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1138" s="8"/>
       <c r="B1138" s="9"/>
     </row>
-    <row r="1139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1139" s="8"/>
       <c r="B1139" s="9"/>
     </row>
-    <row r="1140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1140" s="8"/>
       <c r="B1140" s="9"/>
     </row>
-    <row r="1141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1141" s="8"/>
       <c r="B1141" s="9"/>
     </row>
-    <row r="1142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1142" s="8"/>
       <c r="B1142" s="9"/>
     </row>
-    <row r="1143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1143" s="8"/>
       <c r="B1143" s="9"/>
     </row>
-    <row r="1144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1144" s="8"/>
       <c r="B1144" s="9"/>
     </row>
-    <row r="1145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1145" s="8"/>
       <c r="B1145" s="9"/>
     </row>
-    <row r="1146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1146" s="8"/>
       <c r="B1146" s="9"/>
     </row>
-    <row r="1147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1147" s="8"/>
       <c r="B1147" s="9"/>
     </row>
-    <row r="1148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1148" s="8"/>
       <c r="B1148" s="9"/>
     </row>
-    <row r="1149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1149" s="8"/>
       <c r="B1149" s="9"/>
     </row>
-    <row r="1150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1150" s="8"/>
       <c r="B1150" s="9"/>
     </row>
-    <row r="1151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1151" s="8"/>
       <c r="B1151" s="9"/>
     </row>
-    <row r="1152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1152" s="8"/>
       <c r="B1152" s="9"/>
     </row>
-    <row r="1153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1153" s="8"/>
       <c r="B1153" s="9"/>
     </row>
-    <row r="1154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1154" s="8"/>
       <c r="B1154" s="9"/>
     </row>
-    <row r="1155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1155" s="8"/>
       <c r="B1155" s="9"/>
     </row>
-    <row r="1156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1156" s="8"/>
       <c r="B1156" s="9"/>
     </row>
-    <row r="1157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1157" s="8"/>
       <c r="B1157" s="9"/>
     </row>
-    <row r="1158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1158" s="8"/>
       <c r="B1158" s="9"/>
     </row>
-    <row r="1159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1159" s="8"/>
       <c r="B1159" s="9"/>
     </row>
-    <row r="1160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1160" s="8"/>
       <c r="B1160" s="9"/>
     </row>
-    <row r="1161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1161" s="8"/>
       <c r="B1161" s="9"/>
     </row>
-    <row r="1162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1162" s="8"/>
       <c r="B1162" s="9"/>
     </row>
-    <row r="1163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1163" s="8"/>
       <c r="B1163" s="9"/>
     </row>
-    <row r="1164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1164" s="8"/>
       <c r="B1164" s="9"/>
     </row>
-    <row r="1165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1165" s="8"/>
       <c r="B1165" s="9"/>
     </row>
-    <row r="1166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1166" s="8"/>
       <c r="B1166" s="9"/>
     </row>
-    <row r="1167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1167" s="8"/>
       <c r="B1167" s="9"/>
     </row>
-    <row r="1168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1168" s="8"/>
       <c r="B1168" s="9"/>
     </row>
-    <row r="1169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1169" s="8"/>
       <c r="B1169" s="9"/>
     </row>
-    <row r="1170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1170" s="8"/>
       <c r="B1170" s="9"/>
     </row>
-    <row r="1171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1171" s="8"/>
       <c r="B1171" s="9"/>
     </row>
-    <row r="1172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1172" s="8"/>
       <c r="B1172" s="9"/>
     </row>
-    <row r="1173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1173" s="8"/>
       <c r="B1173" s="9"/>
     </row>
-    <row r="1174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1174" s="8"/>
       <c r="B1174" s="9"/>
     </row>
-    <row r="1175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1175" s="8"/>
       <c r="B1175" s="9"/>
     </row>
-    <row r="1176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1176" s="8"/>
       <c r="B1176" s="9"/>
     </row>
-    <row r="1177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1177" s="8"/>
       <c r="B1177" s="9"/>
     </row>
-    <row r="1178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1178" s="8"/>
       <c r="B1178" s="9"/>
     </row>
-    <row r="1179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1179" s="8"/>
       <c r="B1179" s="9"/>
     </row>
-    <row r="1180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1180" s="8"/>
       <c r="B1180" s="9"/>
     </row>
-    <row r="1181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1181" s="8"/>
       <c r="B1181" s="9"/>
     </row>
-    <row r="1182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1182" s="8"/>
       <c r="B1182" s="9"/>
     </row>
-    <row r="1183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1183" s="8"/>
       <c r="B1183" s="9"/>
     </row>
-    <row r="1184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1184" s="8"/>
       <c r="B1184" s="9"/>
     </row>
-    <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1185" s="8"/>
       <c r="B1185" s="9"/>
     </row>
-    <row r="1186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1186" s="8"/>
       <c r="B1186" s="9"/>
     </row>
-    <row r="1187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1187" s="8"/>
       <c r="B1187" s="9"/>
     </row>
-    <row r="1188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1188" s="8"/>
       <c r="B1188" s="9"/>
     </row>
-    <row r="1189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1189" s="8"/>
       <c r="B1189" s="9"/>
     </row>
-    <row r="1190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1190" s="8"/>
       <c r="B1190" s="9"/>
     </row>
-    <row r="1191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1191" s="8"/>
       <c r="B1191" s="9"/>
     </row>
-    <row r="1192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1192" s="8"/>
       <c r="B1192" s="9"/>
     </row>
-    <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1193" s="8"/>
       <c r="B1193" s="9"/>
     </row>
-    <row r="1194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1194" s="8"/>
       <c r="B1194" s="9"/>
     </row>
-    <row r="1195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1195" s="8"/>
       <c r="B1195" s="9"/>
     </row>
-    <row r="1196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1196" s="8"/>
       <c r="B1196" s="9"/>
     </row>
-    <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1197" s="8"/>
       <c r="B1197" s="9"/>
     </row>
-    <row r="1198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1198" s="8"/>
       <c r="B1198" s="9"/>
     </row>
-    <row r="1199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1199" s="8"/>
       <c r="B1199" s="9"/>
     </row>
-    <row r="1200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1200" s="8"/>
       <c r="B1200" s="9"/>
     </row>
-    <row r="1201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1201" s="8"/>
       <c r="B1201" s="9"/>
     </row>
-    <row r="1202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1202" s="8"/>
       <c r="B1202" s="9"/>
     </row>
-    <row r="1203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1203" s="8"/>
       <c r="B1203" s="9"/>
     </row>
-    <row r="1204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1204" s="8"/>
       <c r="B1204" s="9"/>
     </row>
-    <row r="1205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1205" s="8"/>
       <c r="B1205" s="9"/>
     </row>
-    <row r="1206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1206" s="8"/>
       <c r="B1206" s="9"/>
     </row>
-    <row r="1207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1207" s="8"/>
       <c r="B1207" s="9"/>
     </row>
-    <row r="1208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1208" s="8"/>
       <c r="B1208" s="9"/>
     </row>
-    <row r="1209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1209" s="8"/>
       <c r="B1209" s="9"/>
     </row>
-    <row r="1210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1210" s="8"/>
       <c r="B1210" s="9"/>
     </row>
-    <row r="1211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1211" s="8"/>
       <c r="B1211" s="9"/>
     </row>
-    <row r="1212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1212" s="8"/>
       <c r="B1212" s="9"/>
     </row>
-    <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1213" s="8"/>
       <c r="B1213" s="9"/>
     </row>
-    <row r="1214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1214" s="8"/>
       <c r="B1214" s="9"/>
     </row>
-    <row r="1215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1215" s="8"/>
       <c r="B1215" s="9"/>
     </row>
-    <row r="1216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1216" s="8"/>
       <c r="B1216" s="9"/>
     </row>
-    <row r="1217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1217" s="8"/>
       <c r="B1217" s="9"/>
     </row>
-    <row r="1218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1218" s="8"/>
       <c r="B1218" s="9"/>
     </row>
-    <row r="1219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1219" s="8"/>
       <c r="B1219" s="9"/>
     </row>
-    <row r="1220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1220" s="8"/>
       <c r="B1220" s="9"/>
     </row>
-    <row r="1221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1221" s="8"/>
       <c r="B1221" s="9"/>
     </row>
-    <row r="1222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1222" s="8"/>
       <c r="B1222" s="9"/>
     </row>
-    <row r="1223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1223" s="8"/>
       <c r="B1223" s="9"/>
     </row>
-    <row r="1224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1224" s="8"/>
       <c r="B1224" s="9"/>
     </row>
-    <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1225" s="8"/>
       <c r="B1225" s="9"/>
     </row>
-    <row r="1226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1226" s="8"/>
       <c r="B1226" s="9"/>
     </row>
-    <row r="1227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1227" s="8"/>
       <c r="B1227" s="9"/>
     </row>
-    <row r="1228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1228" s="8"/>
       <c r="B1228" s="9"/>
     </row>
-    <row r="1229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1229" s="8"/>
       <c r="B1229" s="9"/>
     </row>
-    <row r="1230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1230" s="8"/>
       <c r="B1230" s="9"/>
     </row>
-    <row r="1231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1231" s="8"/>
       <c r="B1231" s="9"/>
     </row>
-    <row r="1232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1232" s="8"/>
       <c r="B1232" s="9"/>
     </row>
-    <row r="1233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1233" s="8"/>
       <c r="B1233" s="9"/>
     </row>
-    <row r="1234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1234" s="8"/>
       <c r="B1234" s="9"/>
     </row>
-    <row r="1235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1235" s="8"/>
       <c r="B1235" s="9"/>
     </row>
-    <row r="1236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1236" s="8"/>
       <c r="B1236" s="9"/>
     </row>
-    <row r="1237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1237" s="8"/>
       <c r="B1237" s="9"/>
     </row>
-    <row r="1238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1238" s="8"/>
       <c r="B1238" s="9"/>
     </row>
-    <row r="1239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1239" s="8"/>
       <c r="B1239" s="9"/>
     </row>
-    <row r="1240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1240" s="8"/>
       <c r="B1240" s="9"/>
     </row>
-    <row r="1241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1241" s="8"/>
       <c r="B1241" s="9"/>
     </row>
-    <row r="1242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1242" s="8"/>
       <c r="B1242" s="9"/>
     </row>
-    <row r="1243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1243" s="8"/>
       <c r="B1243" s="9"/>
     </row>
-    <row r="1244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1244" s="8"/>
       <c r="B1244" s="9"/>
     </row>
-    <row r="1245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1245" s="8"/>
       <c r="B1245" s="9"/>
     </row>
-    <row r="1246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1246" s="8"/>
       <c r="B1246" s="9"/>
     </row>
-    <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1247" s="8"/>
       <c r="B1247" s="9"/>
     </row>
-    <row r="1248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1248" s="8"/>
       <c r="B1248" s="9"/>
     </row>
-    <row r="1249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1249" s="8"/>
       <c r="B1249" s="9"/>
     </row>
-    <row r="1250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1250" s="8"/>
       <c r="B1250" s="9"/>
     </row>
-    <row r="1251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1251" s="8"/>
       <c r="B1251" s="9"/>
     </row>
-    <row r="1252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1252" s="8"/>
       <c r="B1252" s="9"/>
     </row>
-    <row r="1253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1253" s="8"/>
       <c r="B1253" s="9"/>
     </row>
-    <row r="1254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1254" s="8"/>
       <c r="B1254" s="9"/>
     </row>
-    <row r="1255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1255" s="8"/>
       <c r="B1255" s="9"/>
     </row>
-    <row r="1256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1256" s="8"/>
       <c r="B1256" s="9"/>
     </row>
-    <row r="1257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1257" s="8"/>
       <c r="B1257" s="9"/>
     </row>
-    <row r="1258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1258" s="8"/>
       <c r="B1258" s="9"/>
     </row>
-    <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1259" s="8"/>
       <c r="B1259" s="9"/>
     </row>
-    <row r="1260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1260" s="8"/>
       <c r="B1260" s="9"/>
     </row>
-    <row r="1261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1261" s="8"/>
       <c r="B1261" s="9"/>
     </row>
-    <row r="1262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1262" s="8"/>
       <c r="B1262" s="9"/>
     </row>
-    <row r="1263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1263" s="8"/>
       <c r="B1263" s="9"/>
     </row>
-    <row r="1264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1264" s="8"/>
       <c r="B1264" s="9"/>
     </row>
-    <row r="1265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1265" s="8"/>
       <c r="B1265" s="9"/>
     </row>
-    <row r="1266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1266" s="8"/>
       <c r="B1266" s="9"/>
     </row>
-    <row r="1267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1267" s="8"/>
       <c r="B1267" s="9"/>
     </row>
-    <row r="1268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1268" s="8"/>
       <c r="B1268" s="9"/>
     </row>
-    <row r="1269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1269" s="8"/>
       <c r="B1269" s="9"/>
     </row>
-    <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1270" s="8"/>
       <c r="B1270" s="9"/>
     </row>
-    <row r="1271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1271" s="8"/>
       <c r="B1271" s="9"/>
     </row>
-    <row r="1272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1272" s="8"/>
       <c r="B1272" s="9"/>
     </row>
-    <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1273" s="8"/>
       <c r="B1273" s="9"/>
     </row>
-    <row r="1274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1274" s="8"/>
       <c r="B1274" s="9"/>
     </row>
-    <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1275" s="8"/>
       <c r="B1275" s="9"/>
     </row>
-    <row r="1276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1276" s="8"/>
       <c r="B1276" s="9"/>
     </row>
-    <row r="1277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1277" s="8"/>
       <c r="B1277" s="9"/>
     </row>
-    <row r="1278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1278" s="8"/>
       <c r="B1278" s="9"/>
     </row>
-    <row r="1279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1279" s="8"/>
       <c r="B1279" s="9"/>
     </row>
-    <row r="1280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1280" s="8"/>
       <c r="B1280" s="9"/>
     </row>
-    <row r="1281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1281" s="8"/>
       <c r="B1281" s="9"/>
     </row>
-    <row r="1282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1282" s="8"/>
       <c r="B1282" s="9"/>
     </row>
-    <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1283" s="8"/>
       <c r="B1283" s="9"/>
     </row>
-    <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1284" s="8"/>
       <c r="B1284" s="9"/>
     </row>
-    <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1285" s="8"/>
       <c r="B1285" s="9"/>
     </row>
-    <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1286" s="8"/>
       <c r="B1286" s="9"/>
     </row>
-    <row r="1287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1287" s="8"/>
       <c r="B1287" s="9"/>
     </row>
-    <row r="1288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1288" s="8"/>
       <c r="B1288" s="9"/>
     </row>
-    <row r="1289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1289" s="8"/>
       <c r="B1289" s="9"/>
     </row>
-    <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1290" s="8"/>
       <c r="B1290" s="9"/>
     </row>
-    <row r="1291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1291" s="8"/>
       <c r="B1291" s="9"/>
     </row>
-    <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1292" s="8"/>
       <c r="B1292" s="9"/>
     </row>
-    <row r="1293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1293" s="8"/>
       <c r="B1293" s="9"/>
     </row>
-    <row r="1294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1294" s="8"/>
       <c r="B1294" s="9"/>
     </row>
-    <row r="1295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1295" s="8"/>
       <c r="B1295" s="9"/>
     </row>
-    <row r="1296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1296" s="8"/>
       <c r="B1296" s="9"/>
     </row>
-    <row r="1297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1297" s="8"/>
       <c r="B1297" s="9"/>
     </row>
-    <row r="1298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1298" s="8"/>
       <c r="B1298" s="9"/>
     </row>
-    <row r="1299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1299" s="8"/>
       <c r="B1299" s="9"/>
     </row>
-    <row r="1300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1300" s="8"/>
       <c r="B1300" s="9"/>
     </row>
-    <row r="1301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1301" s="8"/>
       <c r="B1301" s="9"/>
     </row>
-    <row r="1302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1302" s="8"/>
       <c r="B1302" s="9"/>
     </row>
-    <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1303" s="8"/>
       <c r="B1303" s="9"/>
     </row>
-    <row r="1304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1304" s="8"/>
       <c r="B1304" s="9"/>
     </row>
-    <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1305" s="8"/>
       <c r="B1305" s="9"/>
     </row>
-    <row r="1306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1306" s="8"/>
       <c r="B1306" s="9"/>
     </row>
-    <row r="1307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1307" s="8"/>
       <c r="B1307" s="9"/>
     </row>
-    <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1308" s="8"/>
       <c r="B1308" s="9"/>
     </row>
-    <row r="1309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1309" s="8"/>
       <c r="B1309" s="9"/>
     </row>
-    <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1310" s="8"/>
       <c r="B1310" s="9"/>
     </row>
-    <row r="1311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1311" s="8"/>
       <c r="B1311" s="9"/>
     </row>
-    <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1312" s="8"/>
       <c r="B1312" s="9"/>
     </row>
-    <row r="1313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1313" s="8"/>
       <c r="B1313" s="9"/>
     </row>
-    <row r="1314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1314" s="8"/>
       <c r="B1314" s="9"/>
     </row>
-    <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
     </row>
-    <row r="1316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1316" s="8"/>
       <c r="B1316" s="9"/>
     </row>
-    <row r="1317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1317" s="8"/>
       <c r="B1317" s="9"/>
     </row>
-    <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1318" s="8"/>
       <c r="B1318" s="9"/>
     </row>
-    <row r="1319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1319" s="8"/>
       <c r="B1319" s="9"/>
     </row>
-    <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1320" s="8"/>
       <c r="B1320" s="9"/>
     </row>
-    <row r="1321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1321" s="8"/>
       <c r="B1321" s="9"/>
     </row>
-    <row r="1322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1322" s="8"/>
       <c r="B1322" s="9"/>
     </row>
-    <row r="1323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1323" s="8"/>
       <c r="B1323" s="9"/>
     </row>
-    <row r="1324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1324" s="8"/>
       <c r="B1324" s="9"/>
     </row>
-    <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1325" s="8"/>
       <c r="B1325" s="9"/>
     </row>
-    <row r="1326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1326" s="8"/>
       <c r="B1326" s="9"/>
     </row>
-    <row r="1327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1327" s="8"/>
       <c r="B1327" s="9"/>
     </row>
-    <row r="1328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1328" s="8"/>
       <c r="B1328" s="9"/>
     </row>
-    <row r="1329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1329" s="8"/>
       <c r="B1329" s="9"/>
     </row>
-    <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1330" s="8"/>
       <c r="B1330" s="9"/>
     </row>
-    <row r="1331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1331" s="8"/>
       <c r="B1331" s="9"/>
     </row>
-    <row r="1332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1332" s="8"/>
       <c r="B1332" s="9"/>
     </row>
-    <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1333" s="8"/>
       <c r="B1333" s="9"/>
     </row>
-    <row r="1334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1334" s="8"/>
       <c r="B1334" s="9"/>
     </row>
-    <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1335" s="8"/>
       <c r="B1335" s="9"/>
     </row>
-    <row r="1336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1336" s="8"/>
       <c r="B1336" s="9"/>
     </row>
-    <row r="1337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1337" s="8"/>
       <c r="B1337" s="9"/>
     </row>
-    <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1338" s="8"/>
       <c r="B1338" s="9"/>
     </row>
-    <row r="1339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1339" s="8"/>
       <c r="B1339" s="9"/>
     </row>
-    <row r="1340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1340" s="8"/>
       <c r="B1340" s="9"/>
     </row>
-    <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1341" s="8"/>
       <c r="B1341" s="9"/>
     </row>
-    <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1342" s="8"/>
       <c r="B1342" s="9"/>
     </row>
-    <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1343" s="8"/>
       <c r="B1343" s="9"/>
     </row>
-    <row r="1344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1344" s="8"/>
       <c r="B1344" s="9"/>
     </row>
-    <row r="1345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1345" s="8"/>
       <c r="B1345" s="9"/>
     </row>
-    <row r="1346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1346" s="8"/>
       <c r="B1346" s="9"/>
     </row>
-    <row r="1347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1347" s="8"/>
       <c r="B1347" s="9"/>
     </row>
-    <row r="1348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1348" s="8"/>
       <c r="B1348" s="9"/>
     </row>
-    <row r="1349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1349" s="8"/>
       <c r="B1349" s="9"/>
     </row>
-    <row r="1350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1350" s="8"/>
       <c r="B1350" s="9"/>
     </row>
-    <row r="1351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1351" s="8"/>
       <c r="B1351" s="9"/>
     </row>
-    <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1352" s="8"/>
       <c r="B1352" s="9"/>
     </row>
-    <row r="1353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1353" s="8"/>
       <c r="B1353" s="9"/>
     </row>
-    <row r="1354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1354" s="8"/>
       <c r="B1354" s="9"/>
     </row>
-    <row r="1355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1355" s="8"/>
       <c r="B1355" s="9"/>
     </row>
-    <row r="1356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1356" s="8"/>
       <c r="B1356" s="9"/>
     </row>
-    <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1357" s="8"/>
       <c r="B1357" s="9"/>
     </row>
-    <row r="1358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1358" s="8"/>
       <c r="B1358" s="9"/>
     </row>
-    <row r="1359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1359" s="8"/>
       <c r="B1359" s="9"/>
     </row>
-    <row r="1360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1360" s="8"/>
       <c r="B1360" s="9"/>
     </row>
-    <row r="1361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1361" s="8"/>
       <c r="B1361" s="9"/>
     </row>
-    <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1362" s="8"/>
       <c r="B1362" s="9"/>
     </row>
-    <row r="1363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1363" s="8"/>
       <c r="B1363" s="9"/>
     </row>
-    <row r="1364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1364" s="8"/>
       <c r="B1364" s="9"/>
     </row>
-    <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1365" s="8"/>
       <c r="B1365" s="9"/>
     </row>
-    <row r="1366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1366" s="8"/>
       <c r="B1366" s="9"/>
     </row>
-    <row r="1367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1367" s="8"/>
       <c r="B1367" s="9"/>
     </row>
-    <row r="1368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1368" s="8"/>
       <c r="B1368" s="9"/>
     </row>
-    <row r="1369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1369" s="8"/>
       <c r="B1369" s="9"/>
     </row>
-    <row r="1370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1370" s="8"/>
       <c r="B1370" s="9"/>
     </row>
-    <row r="1371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1371" s="8"/>
       <c r="B1371" s="9"/>
     </row>
-    <row r="1372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1372" s="8"/>
       <c r="B1372" s="9"/>
     </row>
-    <row r="1373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1373" s="8"/>
       <c r="B1373" s="9"/>
     </row>
-    <row r="1374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1374" s="8"/>
       <c r="B1374" s="9"/>
     </row>
-    <row r="1375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1375" s="8"/>
       <c r="B1375" s="9"/>
     </row>
-    <row r="1376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1376" s="8"/>
       <c r="B1376" s="9"/>
     </row>
-    <row r="1377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1377" s="8"/>
       <c r="B1377" s="9"/>
     </row>
-    <row r="1378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1378" s="8"/>
       <c r="B1378" s="9"/>
     </row>
-    <row r="1379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1379" s="8"/>
       <c r="B1379" s="9"/>
     </row>
-    <row r="1380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1380" s="8"/>
       <c r="B1380" s="9"/>
     </row>
-    <row r="1381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1381" s="8"/>
       <c r="B1381" s="9"/>
     </row>
-    <row r="1382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1382" s="8"/>
       <c r="B1382" s="9"/>
     </row>
-    <row r="1383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1383" s="8"/>
       <c r="B1383" s="9"/>
     </row>
-    <row r="1384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1384" s="8"/>
       <c r="B1384" s="9"/>
     </row>
-    <row r="1385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1385" s="8"/>
       <c r="B1385" s="9"/>
     </row>
-    <row r="1386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1386" s="8"/>
       <c r="B1386" s="9"/>
     </row>
-    <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1387" s="8"/>
       <c r="B1387" s="9"/>
     </row>
-    <row r="1388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1388" s="8"/>
       <c r="B1388" s="9"/>
     </row>
-    <row r="1389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1389" s="8"/>
       <c r="B1389" s="9"/>
     </row>
-    <row r="1390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1390" s="8"/>
       <c r="B1390" s="9"/>
     </row>
-    <row r="1391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1391" s="8"/>
       <c r="B1391" s="9"/>
     </row>
-    <row r="1392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1392" s="8"/>
       <c r="B1392" s="9"/>
     </row>
-    <row r="1393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1393" s="8"/>
       <c r="B1393" s="9"/>
     </row>
-    <row r="1394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1394" s="8"/>
       <c r="B1394" s="9"/>
     </row>
-    <row r="1395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1395" s="8"/>
       <c r="B1395" s="9"/>
     </row>
-    <row r="1396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1396" s="8"/>
       <c r="B1396" s="9"/>
     </row>
-    <row r="1397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1397" s="8"/>
       <c r="B1397" s="9"/>
     </row>
-    <row r="1398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1398" s="8"/>
       <c r="B1398" s="9"/>
     </row>
-    <row r="1399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1399" s="8"/>
       <c r="B1399" s="9"/>
     </row>
-    <row r="1400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1400" s="8"/>
       <c r="B1400" s="9"/>
     </row>
-    <row r="1401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1401" s="8"/>
       <c r="B1401" s="9"/>
     </row>
-    <row r="1402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1402" s="8"/>
       <c r="B1402" s="9"/>
     </row>
-    <row r="1403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1403" s="8"/>
       <c r="B1403" s="9"/>
     </row>
-    <row r="1404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1404" s="8"/>
       <c r="B1404" s="9"/>
     </row>
-    <row r="1405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1405" s="8"/>
       <c r="B1405" s="9"/>
     </row>
-    <row r="1406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1406" s="8"/>
       <c r="B1406" s="9"/>
     </row>
-    <row r="1407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1407" s="8"/>
       <c r="B1407" s="9"/>
     </row>
-    <row r="1408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1408" s="8"/>
       <c r="B1408" s="9"/>
     </row>
-    <row r="1409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1409" s="8"/>
       <c r="B1409" s="9"/>
     </row>
-    <row r="1410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1410" s="8"/>
       <c r="B1410" s="9"/>
     </row>
-    <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1411" s="8"/>
       <c r="B1411" s="9"/>
     </row>
-    <row r="1412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1412" s="8"/>
       <c r="B1412" s="9"/>
     </row>
-    <row r="1413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1413" s="8"/>
       <c r="B1413" s="9"/>
     </row>
-    <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1414" s="8"/>
       <c r="B1414" s="9"/>
     </row>
-    <row r="1415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1415" s="8"/>
       <c r="B1415" s="9"/>
     </row>
-    <row r="1416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1416" s="8"/>
       <c r="B1416" s="9"/>
     </row>
-    <row r="1417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1417" s="8"/>
       <c r="B1417" s="9"/>
     </row>
-    <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1418" s="8"/>
       <c r="B1418" s="9"/>
     </row>
-    <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1419" s="8"/>
       <c r="B1419" s="9"/>
     </row>
-    <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1420" s="8"/>
       <c r="B1420" s="9"/>
     </row>
-    <row r="1421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1421" s="8"/>
       <c r="B1421" s="9"/>
     </row>
-    <row r="1422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1422" s="8"/>
       <c r="B1422" s="9"/>
     </row>
-    <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1423" s="8"/>
       <c r="B1423" s="9"/>
     </row>
-    <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1424" s="8"/>
       <c r="B1424" s="9"/>
     </row>
-    <row r="1425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1425" s="8"/>
       <c r="B1425" s="9"/>
     </row>
-    <row r="1426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1426" s="8"/>
       <c r="B1426" s="9"/>
     </row>
-    <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1427" s="8"/>
       <c r="B1427" s="9"/>
     </row>
-    <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1428" s="8"/>
       <c r="B1428" s="9"/>
     </row>
-    <row r="1429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1429" s="8"/>
       <c r="B1429" s="9"/>
     </row>
-    <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1430" s="8"/>
       <c r="B1430" s="9"/>
     </row>
-    <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1431" s="8"/>
       <c r="B1431" s="9"/>
     </row>
-    <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1432" s="8"/>
       <c r="B1432" s="9"/>
     </row>
-    <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1433" s="8"/>
       <c r="B1433" s="9"/>
     </row>
-    <row r="1434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1434" s="8"/>
       <c r="B1434" s="9"/>
     </row>
-    <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1435" s="8"/>
       <c r="B1435" s="9"/>
     </row>
-    <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1436" s="8"/>
       <c r="B1436" s="9"/>
     </row>
-    <row r="1437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1437" s="8"/>
       <c r="B1437" s="9"/>
     </row>
-    <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1438" s="8"/>
       <c r="B1438" s="9"/>
     </row>
-    <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1439" s="8"/>
       <c r="B1439" s="9"/>
     </row>
-    <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1440" s="8"/>
       <c r="B1440" s="9"/>
     </row>
-    <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1441" s="8"/>
       <c r="B1441" s="9"/>
     </row>
-    <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1442" s="8"/>
       <c r="B1442" s="9"/>
     </row>
-    <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1443" s="8"/>
       <c r="B1443" s="9"/>
     </row>
-    <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1444" s="8"/>
       <c r="B1444" s="9"/>
     </row>
-    <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1445" s="8"/>
       <c r="B1445" s="9"/>
     </row>
-    <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1446" s="8"/>
       <c r="B1446" s="9"/>
     </row>
-    <row r="1447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1447" s="8"/>
       <c r="B1447" s="9"/>
     </row>
-    <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1448" s="8"/>
       <c r="B1448" s="9"/>
     </row>
-    <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1449" s="8"/>
       <c r="B1449" s="9"/>
     </row>
-    <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1450" s="8"/>
       <c r="B1450" s="9"/>
     </row>
-    <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1451" s="8"/>
       <c r="B1451" s="9"/>
     </row>
-    <row r="1452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1452" s="8"/>
       <c r="B1452" s="9"/>
     </row>
-    <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1453" s="8"/>
       <c r="B1453" s="9"/>
     </row>
-    <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1454" s="8"/>
       <c r="B1454" s="9"/>
     </row>
-    <row r="1455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1455" s="8"/>
       <c r="B1455" s="9"/>
     </row>
-    <row r="1456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1456" s="8"/>
       <c r="B1456" s="9"/>
     </row>
-    <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1457" s="8"/>
       <c r="B1457" s="9"/>
     </row>
-    <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1458" s="8"/>
       <c r="B1458" s="9"/>
     </row>
-    <row r="1459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1459" s="8"/>
       <c r="B1459" s="9"/>
     </row>
-    <row r="1460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1460" s="8"/>
       <c r="B1460" s="9"/>
     </row>
-    <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1461" s="8"/>
       <c r="B1461" s="9"/>
     </row>
-    <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1462" s="8"/>
       <c r="B1462" s="9"/>
     </row>
-    <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1463" s="8"/>
       <c r="B1463" s="9"/>
     </row>
-    <row r="1464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1464" s="8"/>
       <c r="B1464" s="9"/>
     </row>
-    <row r="1465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1465" s="8"/>
       <c r="B1465" s="9"/>
     </row>
-    <row r="1466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1466" s="8"/>
       <c r="B1466" s="9"/>
     </row>
-    <row r="1467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1467" s="8"/>
       <c r="B1467" s="9"/>
     </row>
-    <row r="1468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1468" s="8"/>
       <c r="B1468" s="9"/>
     </row>
-    <row r="1469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1469" s="8"/>
       <c r="B1469" s="9"/>
     </row>
-    <row r="1470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1470" s="8"/>
       <c r="B1470" s="9"/>
     </row>
-    <row r="1471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1471" s="8"/>
       <c r="B1471" s="9"/>
     </row>
-    <row r="1472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1472" s="8"/>
       <c r="B1472" s="9"/>
     </row>
-    <row r="1473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1473" s="8"/>
       <c r="B1473" s="9"/>
     </row>
-    <row r="1474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1474" s="8"/>
       <c r="B1474" s="9"/>
     </row>
-    <row r="1475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1475" s="8"/>
       <c r="B1475" s="9"/>
     </row>
-    <row r="1476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1476" s="8"/>
       <c r="B1476" s="9"/>
     </row>
-    <row r="1477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1477" s="8"/>
       <c r="B1477" s="9"/>
     </row>
-    <row r="1478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1478" s="8"/>
       <c r="B1478" s="9"/>
     </row>
-    <row r="1479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1479" s="8"/>
       <c r="B1479" s="9"/>
     </row>
-    <row r="1480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1480" s="8"/>
       <c r="B1480" s="9"/>
     </row>
-    <row r="1481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1481" s="8"/>
       <c r="B1481" s="9"/>
     </row>
-    <row r="1482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1482" s="8"/>
       <c r="B1482" s="9"/>
     </row>
-    <row r="1483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1483" s="8"/>
       <c r="B1483" s="9"/>
     </row>
-    <row r="1484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1484" s="8"/>
       <c r="B1484" s="9"/>
     </row>
-    <row r="1485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1485" s="8"/>
       <c r="B1485" s="9"/>
     </row>
-    <row r="1486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1486" s="8"/>
       <c r="B1486" s="9"/>
     </row>
-    <row r="1487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1487" s="10"/>
       <c r="B1487" s="11"/>
     </row>
-    <row r="1488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1488" s="32" t="s">
         <v>159</v>
       </c>
       <c r="B1488" s="33"/>
     </row>
-    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1489" s="34"/>
       <c r="B1489" s="35"/>
     </row>
-    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1490" s="34"/>
       <c r="B1490" s="35"/>
     </row>
-    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1491" s="34"/>
       <c r="B1491" s="35"/>
     </row>
-    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1492" s="34"/>
       <c r="B1492" s="35"/>
     </row>
-    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1493" s="34"/>
       <c r="B1493" s="35"/>
     </row>
-    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1494" s="34"/>
       <c r="B1494" s="35"/>
     </row>
-    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1495" s="34"/>
       <c r="B1495" s="35"/>
     </row>
-    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1496" s="34"/>
       <c r="B1496" s="35"/>
     </row>
-    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1497" s="34"/>
       <c r="B1497" s="35"/>
     </row>
-    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1498" s="34"/>
       <c r="B1498" s="35"/>
     </row>
-    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1499" s="34"/>
       <c r="B1499" s="35"/>
     </row>
-    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1500" s="34"/>
       <c r="B1500" s="35"/>
     </row>
-    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1501" s="34"/>
       <c r="B1501" s="35"/>
     </row>
-    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1502" s="34"/>
       <c r="B1502" s="35"/>
     </row>
-    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1503" s="34"/>
       <c r="B1503" s="35"/>
     </row>
-    <row r="1504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1504" s="34"/>
       <c r="B1504" s="35"/>
     </row>
-    <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1505" s="34"/>
       <c r="B1505" s="35"/>
     </row>
-    <row r="1506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1506" s="34"/>
       <c r="B1506" s="35"/>
     </row>
-    <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1507" s="34"/>
       <c r="B1507" s="35"/>
     </row>
-    <row r="1508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1508" s="34"/>
       <c r="B1508" s="35"/>
     </row>
-    <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1509" s="34"/>
       <c r="B1509" s="35"/>
     </row>
-    <row r="1510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1510" s="34"/>
       <c r="B1510" s="35"/>
     </row>
-    <row r="1511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1511" s="34"/>
       <c r="B1511" s="35"/>
     </row>
-    <row r="1512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1512" s="34"/>
       <c r="B1512" s="35"/>
     </row>
-    <row r="1513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1513" s="34"/>
       <c r="B1513" s="35"/>
     </row>
-    <row r="1514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1514" s="34"/>
       <c r="B1514" s="35"/>
     </row>
-    <row r="1515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1515" s="34"/>
       <c r="B1515" s="35"/>
     </row>
-    <row r="1516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1516" s="34"/>
       <c r="B1516" s="35"/>
     </row>
-    <row r="1517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1517" s="34"/>
       <c r="B1517" s="35"/>
     </row>
-    <row r="1518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1518" s="34"/>
       <c r="B1518" s="35"/>
     </row>
-    <row r="1519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1519" s="34"/>
       <c r="B1519" s="35"/>
     </row>
-    <row r="1520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1520" s="34"/>
       <c r="B1520" s="35"/>
     </row>
-    <row r="1521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1521" s="34"/>
       <c r="B1521" s="35"/>
     </row>
-    <row r="1522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1522" s="34"/>
       <c r="B1522" s="35"/>
     </row>
-    <row r="1523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1523" s="34"/>
       <c r="B1523" s="35"/>
     </row>
-    <row r="1524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1524" s="34"/>
       <c r="B1524" s="35"/>
     </row>
-    <row r="1525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1525" s="34"/>
       <c r="B1525" s="35"/>
     </row>
-    <row r="1526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1526" s="34"/>
       <c r="B1526" s="35"/>
     </row>
-    <row r="1527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1527" s="34"/>
       <c r="B1527" s="35"/>
     </row>
-    <row r="1528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1528" s="34"/>
       <c r="B1528" s="35"/>
     </row>
-    <row r="1529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1529" s="34"/>
       <c r="B1529" s="35"/>
     </row>
-    <row r="1530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1530" s="34"/>
       <c r="B1530" s="35"/>
     </row>
-    <row r="1531" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1531" s="34"/>
       <c r="B1531" s="35"/>
     </row>
-    <row r="1532" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1532" s="34"/>
       <c r="B1532" s="35"/>
     </row>
-    <row r="1533" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1533" s="34"/>
       <c r="B1533" s="35"/>
     </row>
-    <row r="1534" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1534" s="34"/>
       <c r="B1534" s="35"/>
     </row>
-    <row r="1535" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1535" s="34"/>
       <c r="B1535" s="35"/>
     </row>
-    <row r="1536" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1536" s="34"/>
       <c r="B1536" s="35"/>
     </row>
-    <row r="1537" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1537" s="34"/>
       <c r="B1537" s="35"/>
     </row>
-    <row r="1538" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1538" s="34"/>
       <c r="B1538" s="35"/>
     </row>
-    <row r="1539" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1539" s="34"/>
       <c r="B1539" s="35"/>
     </row>
-    <row r="1540" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1540" s="34"/>
       <c r="B1540" s="35"/>
     </row>
-    <row r="1541" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1541" s="36"/>
       <c r="B1541" s="37"/>
     </row>
-    <row r="1542" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1542" s="31"/>
       <c r="B1542" s="27"/>
     </row>

--- a/data/New Microsoft Excel Worksheet.xlsx
+++ b/data/New Microsoft Excel Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B795BBC-29DB-4232-997E-53A36DCE9072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BE2888-D9BC-4A4C-80B8-840BAE8152C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -399,39 +399,21 @@
     <t>MÜH. D-E BLOK-K2-1-DERSLİK</t>
   </si>
   <si>
-    <t>D-201</t>
-  </si>
-  <si>
     <t>MÜH. D-E BLOK-K2-2-DERSLİK</t>
   </si>
   <si>
-    <t>D-202</t>
-  </si>
-  <si>
     <t>MÜH. D-E BLOK-K2-3-DERSLİK</t>
   </si>
   <si>
-    <t>D-203</t>
-  </si>
-  <si>
     <t>MÜH. D-E BLOK-K2-7-DERSLİK</t>
   </si>
   <si>
-    <t>D-204</t>
-  </si>
-  <si>
     <t>MÜH. D-E BLOK-K2-8-DERSLİK</t>
   </si>
   <si>
-    <t>D-205</t>
-  </si>
-  <si>
     <t>MÜH. D-E BLOK-K2-9-DERSLİK</t>
   </si>
   <si>
-    <t>D-206</t>
-  </si>
-  <si>
     <t>ES-K3-13</t>
   </si>
   <si>
@@ -531,75 +513,15 @@
     <t>SERİK</t>
   </si>
   <si>
-    <t>Ylab-2</t>
-  </si>
-  <si>
     <t>BZ01</t>
   </si>
   <si>
-    <t>Ylab-1</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>Amfi03</t>
-  </si>
-  <si>
-    <t>Amfi04</t>
-  </si>
-  <si>
-    <t>C-209</t>
-  </si>
-  <si>
-    <t>C-210</t>
-  </si>
-  <si>
-    <t>C-211</t>
-  </si>
-  <si>
-    <t>C-208</t>
-  </si>
-  <si>
-    <t>C-207</t>
-  </si>
-  <si>
-    <t>C-206</t>
-  </si>
-  <si>
-    <t>C-205</t>
-  </si>
-  <si>
-    <t>C-204</t>
-  </si>
-  <si>
-    <t>C-203</t>
-  </si>
-  <si>
-    <t>C-202</t>
-  </si>
-  <si>
-    <t>C-201</t>
-  </si>
-  <si>
-    <t>B-102</t>
-  </si>
-  <si>
     <t>DZ01</t>
   </si>
   <si>
-    <t>C-212</t>
-  </si>
-  <si>
-    <t>C-213</t>
-  </si>
-  <si>
     <t>BB04</t>
   </si>
   <si>
-    <t>Ylab-3</t>
-  </si>
-  <si>
     <t>Capacity</t>
   </si>
   <si>
@@ -610,6 +532,84 @@
   </si>
   <si>
     <t>Lab</t>
+  </si>
+  <si>
+    <t>YLAB 2</t>
+  </si>
+  <si>
+    <t>C201</t>
+  </si>
+  <si>
+    <t>C202</t>
+  </si>
+  <si>
+    <t>C203</t>
+  </si>
+  <si>
+    <t>C204</t>
+  </si>
+  <si>
+    <t>C212</t>
+  </si>
+  <si>
+    <t>C205</t>
+  </si>
+  <si>
+    <t>C206</t>
+  </si>
+  <si>
+    <t>C207</t>
+  </si>
+  <si>
+    <t>C208</t>
+  </si>
+  <si>
+    <t>C213</t>
+  </si>
+  <si>
+    <t>C209</t>
+  </si>
+  <si>
+    <t>C210</t>
+  </si>
+  <si>
+    <t>C211</t>
+  </si>
+  <si>
+    <t>Amfi 4</t>
+  </si>
+  <si>
+    <t>Amfi 3</t>
+  </si>
+  <si>
+    <t>YLAB 1</t>
+  </si>
+  <si>
+    <t>B102</t>
+  </si>
+  <si>
+    <t>CAD1</t>
+  </si>
+  <si>
+    <t>YLAB 3</t>
+  </si>
+  <si>
+    <t>D201</t>
+  </si>
+  <si>
+    <t>D202</t>
+  </si>
+  <si>
+    <t>D203</t>
+  </si>
+  <si>
+    <t>D204</t>
+  </si>
+  <si>
+    <t>D205</t>
+  </si>
+  <si>
+    <t>D206</t>
   </si>
 </sst>
 </file>
@@ -882,18 +882,6 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
@@ -907,27 +895,19 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -952,6 +932,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1243,15 +1243,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="27"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="24"/>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1259,10 +1259,10 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -1271,7 +1271,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
@@ -1282,32 +1282,32 @@
       <c r="O1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="27"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="24"/>
       <c r="S1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="27"/>
+      <c r="U1" s="24"/>
       <c r="V1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="26"/>
       <c r="F2" s="4" t="s">
         <v>66</v>
       </c>
@@ -1336,28 +1336,28 @@
       <c r="O2" s="7">
         <v>11.25</v>
       </c>
-      <c r="P2" s="30">
+      <c r="P2" s="33">
         <v>16</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="27"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="24"/>
       <c r="S2" s="7">
         <v>2.98</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="33">
         <v>536.4</v>
       </c>
-      <c r="U2" s="27"/>
+      <c r="U2" s="24"/>
       <c r="V2" s="7">
         <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
       <c r="F3" s="4" t="s">
         <v>68</v>
       </c>
@@ -1386,28 +1386,28 @@
       <c r="O3" s="7">
         <v>11.25</v>
       </c>
-      <c r="P3" s="30">
+      <c r="P3" s="33">
         <v>16</v>
       </c>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="27"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="24"/>
       <c r="S3" s="7">
         <v>2.98</v>
       </c>
-      <c r="T3" s="30">
+      <c r="T3" s="33">
         <v>536.4</v>
       </c>
-      <c r="U3" s="27"/>
+      <c r="U3" s="24"/>
       <c r="V3" s="7">
         <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="23"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
       <c r="F4" s="4" t="s">
         <v>35</v>
       </c>
@@ -1436,28 +1436,28 @@
       <c r="O4" s="7">
         <v>14.86</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="33">
         <v>6.93</v>
       </c>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="27"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="24"/>
       <c r="S4" s="7">
         <v>3.37</v>
       </c>
-      <c r="T4" s="30">
+      <c r="T4" s="33">
         <v>347.04199999999997</v>
       </c>
-      <c r="U4" s="27"/>
+      <c r="U4" s="24"/>
       <c r="V4" s="7">
         <v>102.98</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A5" s="23"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="4" t="s">
         <v>71</v>
       </c>
@@ -1465,10 +1465,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>29</v>
@@ -1488,28 +1488,28 @@
       <c r="O5" s="7">
         <v>18.46</v>
       </c>
-      <c r="P5" s="30">
+      <c r="P5" s="33">
         <v>6.9</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="27"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="24"/>
       <c r="S5" s="7">
         <v>2.91</v>
       </c>
-      <c r="T5" s="30">
+      <c r="T5" s="33">
         <v>370.65800000000002</v>
       </c>
-      <c r="U5" s="27"/>
+      <c r="U5" s="24"/>
       <c r="V5" s="7">
         <v>127.374</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A6" s="23"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="4" t="s">
         <v>73</v>
       </c>
@@ -1538,28 +1538,28 @@
       <c r="O6" s="7">
         <v>18.079999999999998</v>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="33">
         <v>6.91</v>
       </c>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="27"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="24"/>
       <c r="S6" s="7">
         <v>2.89</v>
       </c>
-      <c r="T6" s="30">
+      <c r="T6" s="33">
         <v>361.05599999999998</v>
       </c>
-      <c r="U6" s="27"/>
+      <c r="U6" s="24"/>
       <c r="V6" s="7">
         <v>124.93300000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
       <c r="F7" s="4" t="s">
         <v>75</v>
       </c>
@@ -1588,28 +1588,28 @@
       <c r="O7" s="7">
         <v>17.88</v>
       </c>
-      <c r="P7" s="30">
+      <c r="P7" s="33">
         <v>6.75</v>
       </c>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="27"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="24"/>
       <c r="S7" s="7">
         <v>2.9</v>
       </c>
-      <c r="T7" s="30">
+      <c r="T7" s="33">
         <v>350.00099999999998</v>
       </c>
-      <c r="U7" s="27"/>
+      <c r="U7" s="24"/>
       <c r="V7" s="7">
         <v>120.69</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A8" s="23"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="4" t="s">
         <v>30</v>
       </c>
@@ -1638,28 +1638,28 @@
       <c r="O8" s="7">
         <v>14.93</v>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="33">
         <v>6.73</v>
       </c>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="27"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="24"/>
       <c r="S8" s="7">
         <v>2.95</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="33">
         <v>296.41300000000001</v>
       </c>
-      <c r="U8" s="27"/>
+      <c r="U8" s="24"/>
       <c r="V8" s="7">
         <v>100.479</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1688,28 +1688,28 @@
       <c r="O9" s="7">
         <v>6.7</v>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="33">
         <v>10.95</v>
       </c>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="27"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="24"/>
       <c r="S9" s="7">
         <v>2.95</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="33">
         <v>216.42699999999999</v>
       </c>
-      <c r="U9" s="27"/>
+      <c r="U9" s="24"/>
       <c r="V9" s="7">
         <v>73.364999999999995</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="23"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>79</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>14</v>
@@ -1740,28 +1740,28 @@
       <c r="O10" s="7">
         <v>6.7</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10" s="33">
         <v>7.3</v>
       </c>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="27"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="24"/>
       <c r="S10" s="7">
         <v>2.9</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10" s="33">
         <v>141.839</v>
       </c>
-      <c r="U10" s="27"/>
+      <c r="U10" s="24"/>
       <c r="V10" s="7">
         <v>48.91</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
       <c r="F11" s="4" t="s">
         <v>59</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>14</v>
@@ -1792,28 +1792,28 @@
       <c r="O11" s="7">
         <v>10.95</v>
       </c>
-      <c r="P11" s="30">
+      <c r="P11" s="33">
         <v>6.7</v>
       </c>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="27"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="24"/>
       <c r="S11" s="7">
         <v>2.9</v>
       </c>
-      <c r="T11" s="30">
+      <c r="T11" s="33">
         <v>212.75899999999999</v>
       </c>
-      <c r="U11" s="27"/>
+      <c r="U11" s="24"/>
       <c r="V11" s="7">
         <v>73.364999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>81</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>14</v>
@@ -1844,28 +1844,28 @@
       <c r="O12" s="7">
         <v>10.95</v>
       </c>
-      <c r="P12" s="30">
+      <c r="P12" s="33">
         <v>6.75</v>
       </c>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="27"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="24"/>
       <c r="S12" s="7">
         <v>2.9</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="33">
         <v>214.346</v>
       </c>
-      <c r="U12" s="27"/>
+      <c r="U12" s="24"/>
       <c r="V12" s="7">
         <v>73.912999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="23"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4" t="s">
         <v>52</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>82</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>14</v>
@@ -1896,28 +1896,28 @@
       <c r="O13" s="7">
         <v>10.25</v>
       </c>
-      <c r="P13" s="30">
+      <c r="P13" s="33">
         <v>6.7</v>
       </c>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="27"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="24"/>
       <c r="S13" s="7">
         <v>2.9</v>
       </c>
-      <c r="T13" s="30">
+      <c r="T13" s="33">
         <v>199.15799999999999</v>
       </c>
-      <c r="U13" s="27"/>
+      <c r="U13" s="24"/>
       <c r="V13" s="7">
         <v>68.674999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A14" s="23"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4" t="s">
         <v>83</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>84</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>14</v>
@@ -1948,28 +1948,28 @@
       <c r="O14" s="7">
         <v>7.25</v>
       </c>
-      <c r="P14" s="30">
+      <c r="P14" s="33">
         <v>7.25</v>
       </c>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="27"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="24"/>
       <c r="S14" s="7">
         <v>2.9</v>
       </c>
-      <c r="T14" s="30">
+      <c r="T14" s="33">
         <v>152.43100000000001</v>
       </c>
-      <c r="U14" s="27"/>
+      <c r="U14" s="24"/>
       <c r="V14" s="7">
         <v>52.563000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4" t="s">
         <v>42</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>85</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>14</v>
@@ -2000,28 +2000,28 @@
       <c r="O15" s="7">
         <v>6.7</v>
       </c>
-      <c r="P15" s="30">
+      <c r="P15" s="33">
         <v>10.25</v>
       </c>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="27"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="24"/>
       <c r="S15" s="7">
         <v>2.9</v>
       </c>
-      <c r="T15" s="30">
+      <c r="T15" s="33">
         <v>199.15799999999999</v>
       </c>
-      <c r="U15" s="27"/>
+      <c r="U15" s="24"/>
       <c r="V15" s="7">
         <v>68.674999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="23"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="4" t="s">
         <v>43</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>86</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>14</v>
@@ -2052,28 +2052,28 @@
       <c r="O16" s="7">
         <v>6.7</v>
       </c>
-      <c r="P16" s="30">
+      <c r="P16" s="33">
         <v>12.85</v>
       </c>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="27"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="24"/>
       <c r="S16" s="7">
         <v>2.9</v>
       </c>
-      <c r="T16" s="30">
+      <c r="T16" s="33">
         <v>249.67599999999999</v>
       </c>
-      <c r="U16" s="27"/>
+      <c r="U16" s="24"/>
       <c r="V16" s="7">
         <v>86.094999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="4" t="s">
         <v>57</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>87</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>14</v>
@@ -2104,28 +2104,28 @@
       <c r="O17" s="7">
         <v>6.7</v>
       </c>
-      <c r="P17" s="30">
+      <c r="P17" s="33">
         <v>11.05</v>
       </c>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="27"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="24"/>
       <c r="S17" s="7">
         <v>2.9</v>
       </c>
-      <c r="T17" s="30">
+      <c r="T17" s="33">
         <v>214.702</v>
       </c>
-      <c r="U17" s="27"/>
+      <c r="U17" s="24"/>
       <c r="V17" s="7">
         <v>74.034999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="23"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="4" t="s">
         <v>31</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>88</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>14</v>
@@ -2156,28 +2156,28 @@
       <c r="O18" s="7">
         <v>10.24</v>
       </c>
-      <c r="P18" s="30">
+      <c r="P18" s="33">
         <v>6.7</v>
       </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="27"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="24"/>
       <c r="S18" s="7">
         <v>2.9</v>
       </c>
-      <c r="T18" s="30">
+      <c r="T18" s="33">
         <v>198.96299999999999</v>
       </c>
-      <c r="U18" s="27"/>
+      <c r="U18" s="24"/>
       <c r="V18" s="7">
         <v>68.608000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A19" s="23"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
       <c r="F19" s="4" t="s">
         <v>89</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>14</v>
@@ -2208,28 +2208,28 @@
       <c r="O19" s="7">
         <v>7.3</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P19" s="33">
         <v>7.3</v>
       </c>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="27"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="24"/>
       <c r="S19" s="7">
         <v>2.9</v>
       </c>
-      <c r="T19" s="30">
+      <c r="T19" s="33">
         <v>154.541</v>
       </c>
-      <c r="U19" s="27"/>
+      <c r="U19" s="24"/>
       <c r="V19" s="7">
         <v>53.29</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="23"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="4" t="s">
         <v>27</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>14</v>
@@ -2260,28 +2260,28 @@
       <c r="O20" s="7">
         <v>6.7</v>
       </c>
-      <c r="P20" s="30">
+      <c r="P20" s="33">
         <v>10.25</v>
       </c>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="27"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="24"/>
       <c r="S20" s="7">
         <v>2.9</v>
       </c>
-      <c r="T20" s="30">
+      <c r="T20" s="33">
         <v>199.15799999999999</v>
       </c>
-      <c r="U20" s="27"/>
+      <c r="U20" s="24"/>
       <c r="V20" s="7">
         <v>68.674999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="23"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4" t="s">
         <v>61</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>92</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>14</v>
@@ -2312,28 +2312,28 @@
       <c r="O21" s="7">
         <v>6.7</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="33">
         <v>10.95</v>
       </c>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="27"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="24"/>
       <c r="S21" s="7">
         <v>2.9</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="33">
         <v>212.75899999999999</v>
       </c>
-      <c r="U21" s="27"/>
+      <c r="U21" s="24"/>
       <c r="V21" s="7">
         <v>73.364999999999995</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="23"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="4" t="s">
         <v>28</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>93</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>14</v>
@@ -2364,30 +2364,30 @@
       <c r="O22" s="7">
         <v>6.7</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="33">
         <v>11.75</v>
       </c>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="27"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="24"/>
       <c r="S22" s="7">
         <v>2.9</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="33">
         <v>228.303</v>
       </c>
-      <c r="U22" s="27"/>
+      <c r="U22" s="24"/>
       <c r="V22" s="7">
         <v>78.724999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="23"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="23" t="s">
+      <c r="A23" s="20"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="4" t="s">
         <v>62</v>
       </c>
@@ -2418,28 +2418,28 @@
       <c r="O23" s="7">
         <v>18.649999999999999</v>
       </c>
-      <c r="P23" s="30">
+      <c r="P23" s="33">
         <v>6.65</v>
       </c>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="27"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="24"/>
       <c r="S23" s="7">
         <v>3.41</v>
       </c>
-      <c r="T23" s="30">
+      <c r="T23" s="33">
         <v>422.91699999999997</v>
       </c>
-      <c r="U23" s="27"/>
+      <c r="U23" s="24"/>
       <c r="V23" s="7">
         <v>124.023</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="23"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
       <c r="F24" s="4" t="s">
         <v>55</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>97</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>14</v>
@@ -2470,28 +2470,28 @@
       <c r="O24" s="7">
         <v>7.47</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="33">
         <v>6.68</v>
       </c>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="27"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="24"/>
       <c r="S24" s="7">
         <v>3.39</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="33">
         <v>169.16</v>
       </c>
-      <c r="U24" s="27"/>
+      <c r="U24" s="24"/>
       <c r="V24" s="7">
         <v>49.9</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="23"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
       <c r="F25" s="4" t="s">
         <v>98</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>99</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>14</v>
@@ -2522,28 +2522,28 @@
       <c r="O25" s="7">
         <v>7.38</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="33">
         <v>6.68</v>
       </c>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="27"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="24"/>
       <c r="S25" s="7">
         <v>3.43</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="33">
         <v>169.09399999999999</v>
       </c>
-      <c r="U25" s="27"/>
+      <c r="U25" s="24"/>
       <c r="V25" s="7">
         <v>49.298000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="23"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="25"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="4" t="s">
         <v>100</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>101</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>14</v>
@@ -2574,28 +2574,28 @@
       <c r="O26" s="7">
         <v>14.92</v>
       </c>
-      <c r="P26" s="30">
+      <c r="P26" s="33">
         <v>6.68</v>
       </c>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="27"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="24"/>
       <c r="S26" s="7">
         <v>3.43</v>
       </c>
-      <c r="T26" s="30">
+      <c r="T26" s="33">
         <v>341.85300000000001</v>
       </c>
-      <c r="U26" s="27"/>
+      <c r="U26" s="24"/>
       <c r="V26" s="7">
         <v>99.665999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="23"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
       <c r="F27" s="4" t="s">
         <v>18</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>102</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>14</v>
@@ -2626,28 +2626,28 @@
       <c r="O27" s="7">
         <v>10.97</v>
       </c>
-      <c r="P27" s="30">
+      <c r="P27" s="33">
         <v>6.64</v>
       </c>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="27"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="24"/>
       <c r="S27" s="7">
         <v>3.31</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="33">
         <v>241.10300000000001</v>
       </c>
-      <c r="U27" s="27"/>
+      <c r="U27" s="24"/>
       <c r="V27" s="7">
         <v>72.840999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A28" s="23"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="25"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
       <c r="F28" s="4" t="s">
         <v>64</v>
       </c>
@@ -2655,10 +2655,10 @@
         <v>103</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>29</v>
@@ -2678,28 +2678,28 @@
       <c r="O28" s="7">
         <v>18.98</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="33">
         <v>6.64</v>
       </c>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="27"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="24"/>
       <c r="S28" s="7">
         <v>3.31</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="33">
         <v>417.15</v>
       </c>
-      <c r="U28" s="27"/>
+      <c r="U28" s="24"/>
       <c r="V28" s="7">
         <v>126.027</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="23"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
       <c r="F29" s="4" t="s">
         <v>21</v>
       </c>
@@ -2728,28 +2728,28 @@
       <c r="O29" s="7">
         <v>11.03</v>
       </c>
-      <c r="P29" s="30">
+      <c r="P29" s="33">
         <v>6.79</v>
       </c>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="27"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="24"/>
       <c r="S29" s="7">
         <v>3.14</v>
       </c>
-      <c r="T29" s="30">
+      <c r="T29" s="33">
         <v>235.166</v>
       </c>
-      <c r="U29" s="27"/>
+      <c r="U29" s="24"/>
       <c r="V29" s="7">
         <v>74.894000000000005</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="23"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
       <c r="F30" s="4" t="s">
         <v>23</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>105</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>14</v>
@@ -2780,30 +2780,30 @@
       <c r="O30" s="7">
         <v>6.77</v>
       </c>
-      <c r="P30" s="30">
+      <c r="P30" s="33">
         <v>11.02</v>
       </c>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="27"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="24"/>
       <c r="S30" s="7">
         <v>2.95</v>
       </c>
-      <c r="T30" s="30">
+      <c r="T30" s="33">
         <v>220.08600000000001</v>
       </c>
-      <c r="U30" s="27"/>
+      <c r="U30" s="24"/>
       <c r="V30" s="7">
         <v>74.605000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A31" s="23"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="23" t="s">
+      <c r="A31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
       <c r="F31" s="4" t="s">
         <v>64</v>
       </c>
@@ -2832,28 +2832,28 @@
       <c r="O31" s="7">
         <v>22.46</v>
       </c>
-      <c r="P31" s="30">
+      <c r="P31" s="33">
         <v>6.68</v>
       </c>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="27"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="24"/>
       <c r="S31" s="7">
         <v>3.25</v>
       </c>
-      <c r="T31" s="30">
+      <c r="T31" s="33">
         <v>487.60700000000003</v>
       </c>
-      <c r="U31" s="27"/>
+      <c r="U31" s="24"/>
       <c r="V31" s="7">
         <v>150.03299999999999</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="23"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
       <c r="F32" s="4" t="s">
         <v>44</v>
       </c>
@@ -2882,28 +2882,28 @@
       <c r="O32" s="7">
         <v>18.75</v>
       </c>
-      <c r="P32" s="30">
+      <c r="P32" s="33">
         <v>6.46</v>
       </c>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="27"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="24"/>
       <c r="S32" s="7">
         <v>3.26</v>
       </c>
-      <c r="T32" s="30">
+      <c r="T32" s="33">
         <v>394.86799999999999</v>
       </c>
-      <c r="U32" s="27"/>
+      <c r="U32" s="24"/>
       <c r="V32" s="7">
         <v>121.125</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="23"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22"/>
       <c r="F33" s="4" t="s">
         <v>16</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>109</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>14</v>
@@ -2934,28 +2934,28 @@
       <c r="O33" s="7">
         <v>13.55</v>
       </c>
-      <c r="P33" s="30">
+      <c r="P33" s="33">
         <v>6.8</v>
       </c>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="27"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="24"/>
       <c r="S33" s="7">
         <v>2.95</v>
       </c>
-      <c r="T33" s="30">
+      <c r="T33" s="33">
         <v>271.81299999999999</v>
       </c>
-      <c r="U33" s="27"/>
+      <c r="U33" s="24"/>
       <c r="V33" s="7">
         <v>92.14</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A34" s="23"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="22"/>
       <c r="F34" s="4" t="s">
         <v>110</v>
       </c>
@@ -2963,10 +2963,10 @@
         <v>111</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>29</v>
@@ -2986,28 +2986,28 @@
       <c r="O34" s="7">
         <v>13.3</v>
       </c>
-      <c r="P34" s="30">
+      <c r="P34" s="33">
         <v>6.8</v>
       </c>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="27"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="24"/>
       <c r="S34" s="7">
         <v>2.95</v>
       </c>
-      <c r="T34" s="30">
+      <c r="T34" s="33">
         <v>266.798</v>
       </c>
-      <c r="U34" s="27"/>
+      <c r="U34" s="24"/>
       <c r="V34" s="7">
         <v>90.44</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A35" s="23"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="25"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="4" t="s">
         <v>54</v>
       </c>
@@ -3036,28 +3036,28 @@
       <c r="O35" s="7">
         <v>2.59</v>
       </c>
-      <c r="P35" s="30">
+      <c r="P35" s="33">
         <v>6.78</v>
       </c>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="27"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="24"/>
       <c r="S35" s="7">
         <v>2.94</v>
       </c>
-      <c r="T35" s="30">
+      <c r="T35" s="33">
         <v>51.627000000000002</v>
       </c>
-      <c r="U35" s="27"/>
+      <c r="U35" s="24"/>
       <c r="V35" s="7">
         <v>17.559999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A36" s="23"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="25"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="22"/>
       <c r="F36" s="4" t="s">
         <v>56</v>
       </c>
@@ -3086,28 +3086,28 @@
       <c r="O36" s="7">
         <v>22.35</v>
       </c>
-      <c r="P36" s="30">
+      <c r="P36" s="33">
         <v>6.85</v>
       </c>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="27"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="24"/>
       <c r="S36" s="7">
         <v>2.94</v>
       </c>
-      <c r="T36" s="30">
+      <c r="T36" s="33">
         <v>450.10700000000003</v>
       </c>
-      <c r="U36" s="27"/>
+      <c r="U36" s="24"/>
       <c r="V36" s="7">
         <v>153.09800000000001</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A37" s="23"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22"/>
       <c r="F37" s="4" t="s">
         <v>73</v>
       </c>
@@ -3115,10 +3115,10 @@
         <v>114</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>29</v>
@@ -3138,28 +3138,28 @@
       <c r="O37" s="7">
         <v>13.55</v>
       </c>
-      <c r="P37" s="30">
+      <c r="P37" s="33">
         <v>6.8</v>
       </c>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="27"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="24"/>
       <c r="S37" s="7">
         <v>2.95</v>
       </c>
-      <c r="T37" s="30">
+      <c r="T37" s="33">
         <v>271.81299999999999</v>
       </c>
-      <c r="U37" s="27"/>
+      <c r="U37" s="24"/>
       <c r="V37" s="7">
         <v>92.14</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="23"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="25"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22"/>
       <c r="F38" s="4" t="s">
         <v>24</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>115</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>14</v>
@@ -3190,36 +3190,36 @@
       <c r="O38" s="7">
         <v>13.22</v>
       </c>
-      <c r="P38" s="30">
+      <c r="P38" s="33">
         <v>6.8</v>
       </c>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="27"/>
+      <c r="Q38" s="34"/>
+      <c r="R38" s="24"/>
       <c r="S38" s="7">
         <v>2.94</v>
       </c>
-      <c r="T38" s="30">
+      <c r="T38" s="33">
         <v>264.29399999999998</v>
       </c>
-      <c r="U38" s="27"/>
+      <c r="U38" s="24"/>
       <c r="V38" s="7">
         <v>89.896000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="23"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="22"/>
       <c r="F39" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>14</v>
@@ -3242,36 +3242,36 @@
       <c r="O39" s="7">
         <v>11.23</v>
       </c>
-      <c r="P39" s="30">
+      <c r="P39" s="33">
         <v>6.8</v>
       </c>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="27"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="24"/>
       <c r="S39" s="7">
         <v>2.94</v>
       </c>
-      <c r="T39" s="30">
+      <c r="T39" s="33">
         <v>224.51</v>
       </c>
-      <c r="U39" s="27"/>
+      <c r="U39" s="24"/>
       <c r="V39" s="7">
         <v>76.364000000000004</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="23"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="25"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22"/>
       <c r="F40" s="4" t="s">
         <v>50</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>14</v>
@@ -3294,36 +3294,36 @@
       <c r="O40" s="7">
         <v>11.19</v>
       </c>
-      <c r="P40" s="30">
+      <c r="P40" s="33">
         <v>6.79</v>
       </c>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="27"/>
+      <c r="Q40" s="34"/>
+      <c r="R40" s="24"/>
       <c r="S40" s="7">
         <v>2.92</v>
       </c>
-      <c r="T40" s="30">
+      <c r="T40" s="33">
         <v>221.86199999999999</v>
       </c>
-      <c r="U40" s="27"/>
+      <c r="U40" s="24"/>
       <c r="V40" s="7">
         <v>75.98</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="23"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="25"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
       <c r="F41" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>14</v>
@@ -3346,36 +3346,36 @@
       <c r="O41" s="7">
         <v>11.13</v>
       </c>
-      <c r="P41" s="30">
+      <c r="P41" s="33">
         <v>6.81</v>
       </c>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="27"/>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="24"/>
       <c r="S41" s="7">
         <v>2.96</v>
       </c>
-      <c r="T41" s="30">
+      <c r="T41" s="33">
         <v>224.35400000000001</v>
       </c>
-      <c r="U41" s="27"/>
+      <c r="U41" s="24"/>
       <c r="V41" s="7">
         <v>75.795000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="23"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="25"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>14</v>
@@ -3398,36 +3398,36 @@
       <c r="O42" s="7">
         <v>10.94</v>
       </c>
-      <c r="P42" s="30">
+      <c r="P42" s="33">
         <v>6.91</v>
       </c>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="27"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="24"/>
       <c r="S42" s="7">
         <v>2.96</v>
       </c>
-      <c r="T42" s="30">
+      <c r="T42" s="33">
         <v>223.762</v>
       </c>
-      <c r="U42" s="27"/>
+      <c r="U42" s="24"/>
       <c r="V42" s="7">
         <v>75.594999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="23"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="25"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22"/>
       <c r="F43" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>14</v>
@@ -3450,33 +3450,33 @@
       <c r="O43" s="7">
         <v>13.62</v>
       </c>
-      <c r="P43" s="30">
+      <c r="P43" s="33">
         <v>6.81</v>
       </c>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="27"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="24"/>
       <c r="S43" s="7">
         <v>2.96</v>
       </c>
-      <c r="T43" s="30">
+      <c r="T43" s="33">
         <v>274.54700000000003</v>
       </c>
-      <c r="U43" s="27"/>
+      <c r="U43" s="24"/>
       <c r="V43" s="7">
         <v>92.751999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="23"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="25"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="22"/>
       <c r="F44" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4" t="s">
@@ -3500,35 +3500,35 @@
       <c r="O44" s="7">
         <v>7.47</v>
       </c>
-      <c r="P44" s="30">
+      <c r="P44" s="33">
         <v>7.37</v>
       </c>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="27"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="24"/>
       <c r="S44" s="7">
         <v>2.64</v>
       </c>
-      <c r="T44" s="30">
+      <c r="T44" s="33">
         <v>145.34200000000001</v>
       </c>
-      <c r="U44" s="27"/>
+      <c r="U44" s="24"/>
       <c r="V44" s="7">
         <v>55.054000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="23"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22"/>
       <c r="F45" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4" t="s">
@@ -3552,33 +3552,33 @@
       <c r="O45" s="7">
         <v>4.87</v>
       </c>
-      <c r="P45" s="30">
+      <c r="P45" s="33">
         <v>7.53</v>
       </c>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="27"/>
+      <c r="Q45" s="34"/>
+      <c r="R45" s="24"/>
       <c r="S45" s="7">
         <v>2.92</v>
       </c>
-      <c r="T45" s="30">
+      <c r="T45" s="33">
         <v>107.08</v>
       </c>
-      <c r="U45" s="27"/>
+      <c r="U45" s="24"/>
       <c r="V45" s="7">
         <v>36.670999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A46" s="23"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="25"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
@@ -3602,33 +3602,33 @@
       <c r="O46" s="7">
         <v>11.33</v>
       </c>
-      <c r="P46" s="30">
+      <c r="P46" s="33">
         <v>8.77</v>
       </c>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="27"/>
+      <c r="Q46" s="34"/>
+      <c r="R46" s="24"/>
       <c r="S46" s="7">
         <v>3.07</v>
       </c>
-      <c r="T46" s="30">
+      <c r="T46" s="33">
         <v>305.048</v>
       </c>
-      <c r="U46" s="27"/>
+      <c r="U46" s="24"/>
       <c r="V46" s="7">
         <v>99.364000000000004</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A47" s="23"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="25"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
@@ -3652,33 +3652,33 @@
       <c r="O47" s="7">
         <v>7.9</v>
       </c>
-      <c r="P47" s="30">
+      <c r="P47" s="33">
         <v>8.85</v>
       </c>
-      <c r="Q47" s="28"/>
-      <c r="R47" s="27"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="24"/>
       <c r="S47" s="7">
         <v>3.07</v>
       </c>
-      <c r="T47" s="30">
+      <c r="T47" s="33">
         <v>214.63900000000001</v>
       </c>
-      <c r="U47" s="27"/>
+      <c r="U47" s="24"/>
       <c r="V47" s="7">
         <v>69.915000000000006</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="23"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22"/>
       <c r="F48" s="4" t="s">
         <v>63</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
@@ -3702,33 +3702,33 @@
       <c r="O48" s="7">
         <v>8</v>
       </c>
-      <c r="P48" s="30">
+      <c r="P48" s="33">
         <v>8.85</v>
       </c>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="27"/>
+      <c r="Q48" s="34"/>
+      <c r="R48" s="24"/>
       <c r="S48" s="7">
         <v>3.07</v>
       </c>
-      <c r="T48" s="30">
+      <c r="T48" s="33">
         <v>217.35599999999999</v>
       </c>
-      <c r="U48" s="27"/>
+      <c r="U48" s="24"/>
       <c r="V48" s="7">
         <v>70.8</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="23"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="25"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="22"/>
       <c r="F49" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4" t="s">
@@ -3752,33 +3752,33 @@
       <c r="O49" s="7">
         <v>7.52</v>
       </c>
-      <c r="P49" s="30">
+      <c r="P49" s="33">
         <v>10.73</v>
       </c>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="27"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="24"/>
       <c r="S49" s="7">
         <v>3.16</v>
       </c>
-      <c r="T49" s="30">
+      <c r="T49" s="33">
         <v>254.97900000000001</v>
       </c>
-      <c r="U49" s="27"/>
+      <c r="U49" s="24"/>
       <c r="V49" s="7">
         <v>80.69</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="23"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="25"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="22"/>
       <c r="F50" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4" t="s">
@@ -3802,33 +3802,33 @@
       <c r="O50" s="7">
         <v>7.54</v>
       </c>
-      <c r="P50" s="30">
+      <c r="P50" s="33">
         <v>10.66</v>
       </c>
-      <c r="Q50" s="28"/>
-      <c r="R50" s="27"/>
+      <c r="Q50" s="34"/>
+      <c r="R50" s="24"/>
       <c r="S50" s="7">
         <v>3.16</v>
       </c>
-      <c r="T50" s="30">
+      <c r="T50" s="33">
         <v>253.989</v>
       </c>
-      <c r="U50" s="27"/>
+      <c r="U50" s="24"/>
       <c r="V50" s="7">
         <v>80.376000000000005</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="23"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="25"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="22"/>
       <c r="F51" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4" t="s">
@@ -3852,33 +3852,33 @@
       <c r="O51" s="7">
         <v>7.59</v>
       </c>
-      <c r="P51" s="30">
+      <c r="P51" s="33">
         <v>11.48</v>
       </c>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="27"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="24"/>
       <c r="S51" s="7">
         <v>3.07</v>
       </c>
-      <c r="T51" s="30">
+      <c r="T51" s="33">
         <v>267.49900000000002</v>
       </c>
-      <c r="U51" s="27"/>
+      <c r="U51" s="24"/>
       <c r="V51" s="7">
         <v>87.132999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="23"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="25"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="22"/>
       <c r="F52" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4" t="s">
@@ -3902,33 +3902,33 @@
       <c r="O52" s="7">
         <v>7.57</v>
       </c>
-      <c r="P52" s="30">
+      <c r="P52" s="33">
         <v>7.74</v>
       </c>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="27"/>
+      <c r="Q52" s="34"/>
+      <c r="R52" s="24"/>
       <c r="S52" s="7">
         <v>3.07</v>
       </c>
-      <c r="T52" s="30">
+      <c r="T52" s="33">
         <v>179.87700000000001</v>
       </c>
-      <c r="U52" s="27"/>
+      <c r="U52" s="24"/>
       <c r="V52" s="7">
         <v>58.591999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="23"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="25"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="22"/>
       <c r="F53" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4" t="s">
@@ -3952,33 +3952,33 @@
       <c r="O53" s="7">
         <v>4.5</v>
       </c>
-      <c r="P53" s="30">
+      <c r="P53" s="33">
         <v>7.77</v>
       </c>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="27"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="24"/>
       <c r="S53" s="7">
         <v>3.21</v>
       </c>
-      <c r="T53" s="30">
+      <c r="T53" s="33">
         <v>112.238</v>
       </c>
-      <c r="U53" s="27"/>
+      <c r="U53" s="24"/>
       <c r="V53" s="7">
         <v>34.965000000000003</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="23"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="25"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="22"/>
       <c r="F54" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4" t="s">
@@ -4002,33 +4002,33 @@
       <c r="O54" s="7">
         <v>7.08</v>
       </c>
-      <c r="P54" s="30">
+      <c r="P54" s="33">
         <v>7</v>
       </c>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="27"/>
+      <c r="Q54" s="34"/>
+      <c r="R54" s="24"/>
       <c r="S54" s="7">
         <v>3.2</v>
       </c>
-      <c r="T54" s="30">
+      <c r="T54" s="33">
         <v>158.59200000000001</v>
       </c>
-      <c r="U54" s="27"/>
+      <c r="U54" s="24"/>
       <c r="V54" s="7">
         <v>49.56</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="23"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="25"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4" t="s">
@@ -4052,33 +4052,33 @@
       <c r="O55" s="7">
         <v>7</v>
       </c>
-      <c r="P55" s="30">
+      <c r="P55" s="33">
         <v>7.8</v>
       </c>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="27"/>
+      <c r="Q55" s="34"/>
+      <c r="R55" s="24"/>
       <c r="S55" s="7">
         <v>3.22</v>
       </c>
-      <c r="T55" s="30">
+      <c r="T55" s="33">
         <v>175.81200000000001</v>
       </c>
-      <c r="U55" s="27"/>
+      <c r="U55" s="24"/>
       <c r="V55" s="7">
         <v>54.6</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="23"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
@@ -4102,33 +4102,33 @@
       <c r="O56" s="7">
         <v>7</v>
       </c>
-      <c r="P56" s="30">
+      <c r="P56" s="33">
         <v>8</v>
       </c>
-      <c r="Q56" s="28"/>
-      <c r="R56" s="27"/>
+      <c r="Q56" s="34"/>
+      <c r="R56" s="24"/>
       <c r="S56" s="7">
         <v>3.22</v>
       </c>
-      <c r="T56" s="30">
+      <c r="T56" s="33">
         <v>180.32</v>
       </c>
-      <c r="U56" s="27"/>
+      <c r="U56" s="24"/>
       <c r="V56" s="7">
         <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A57" s="23"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="25"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="4" t="s">
         <v>47</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
@@ -4152,33 +4152,33 @@
       <c r="O57" s="7">
         <v>7.75</v>
       </c>
-      <c r="P57" s="30">
+      <c r="P57" s="33">
         <v>8.7799999999999994</v>
       </c>
-      <c r="Q57" s="28"/>
-      <c r="R57" s="27"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="24"/>
       <c r="S57" s="7">
         <v>2.97</v>
       </c>
-      <c r="T57" s="30">
+      <c r="T57" s="33">
         <v>202.09399999999999</v>
       </c>
-      <c r="U57" s="27"/>
+      <c r="U57" s="24"/>
       <c r="V57" s="7">
         <v>68.045000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A58" s="23"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="25"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
@@ -4202,33 +4202,33 @@
       <c r="O58" s="7">
         <v>5.54</v>
       </c>
-      <c r="P58" s="30">
+      <c r="P58" s="33">
         <v>8.81</v>
       </c>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="27"/>
+      <c r="Q58" s="34"/>
+      <c r="R58" s="24"/>
       <c r="S58" s="7">
         <v>2.94</v>
       </c>
-      <c r="T58" s="30">
+      <c r="T58" s="33">
         <v>143.494</v>
       </c>
-      <c r="U58" s="27"/>
+      <c r="U58" s="24"/>
       <c r="V58" s="7">
         <v>48.807000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A59" s="23"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="25"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="22"/>
       <c r="F59" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
@@ -4252,33 +4252,33 @@
       <c r="O59" s="7">
         <v>7.5</v>
       </c>
-      <c r="P59" s="30">
+      <c r="P59" s="33">
         <v>10.77</v>
       </c>
-      <c r="Q59" s="28"/>
-      <c r="R59" s="27"/>
+      <c r="Q59" s="34"/>
+      <c r="R59" s="24"/>
       <c r="S59" s="7">
         <v>2.95</v>
       </c>
-      <c r="T59" s="30">
+      <c r="T59" s="33">
         <v>238.286</v>
       </c>
-      <c r="U59" s="27"/>
+      <c r="U59" s="24"/>
       <c r="V59" s="7">
         <v>80.775000000000006</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A60" s="23"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="25"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
@@ -4302,33 +4302,33 @@
       <c r="O60" s="7">
         <v>7.6</v>
       </c>
-      <c r="P60" s="30">
+      <c r="P60" s="33">
         <v>8</v>
       </c>
-      <c r="Q60" s="28"/>
-      <c r="R60" s="27"/>
+      <c r="Q60" s="34"/>
+      <c r="R60" s="24"/>
       <c r="S60" s="7">
         <v>3.11</v>
       </c>
-      <c r="T60" s="30">
+      <c r="T60" s="33">
         <v>189.08799999999999</v>
       </c>
-      <c r="U60" s="27"/>
+      <c r="U60" s="24"/>
       <c r="V60" s="7">
         <v>60.8</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="42" x14ac:dyDescent="0.35">
-      <c r="A61" s="23"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25"/>
+      <c r="A61" s="20"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
@@ -4352,33 +4352,33 @@
       <c r="O61" s="7">
         <v>7.6</v>
       </c>
-      <c r="P61" s="30">
+      <c r="P61" s="33">
         <v>7.78</v>
       </c>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="27"/>
+      <c r="Q61" s="34"/>
+      <c r="R61" s="24"/>
       <c r="S61" s="7">
         <v>3.27</v>
       </c>
-      <c r="T61" s="30">
+      <c r="T61" s="33">
         <v>193.34899999999999</v>
       </c>
-      <c r="U61" s="27"/>
+      <c r="U61" s="24"/>
       <c r="V61" s="7">
         <v>59.128</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A62" s="23"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="25"/>
+      <c r="A62" s="20"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="22"/>
       <c r="F62" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
@@ -4402,33 +4402,33 @@
       <c r="O62" s="7">
         <v>6.18</v>
       </c>
-      <c r="P62" s="30">
+      <c r="P62" s="33">
         <v>7.54</v>
       </c>
-      <c r="Q62" s="28"/>
-      <c r="R62" s="27"/>
+      <c r="Q62" s="34"/>
+      <c r="R62" s="24"/>
       <c r="S62" s="7">
         <v>3.12</v>
       </c>
-      <c r="T62" s="30">
+      <c r="T62" s="33">
         <v>145.38300000000001</v>
       </c>
-      <c r="U62" s="27"/>
+      <c r="U62" s="24"/>
       <c r="V62" s="7">
         <v>46.597000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A63" s="23"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="25"/>
+      <c r="A63" s="20"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="22"/>
       <c r="F63" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
@@ -4452,417 +4452,417 @@
       <c r="O63" s="7">
         <v>4.63</v>
       </c>
-      <c r="P63" s="30">
+      <c r="P63" s="33">
         <v>7.85</v>
       </c>
-      <c r="Q63" s="28"/>
-      <c r="R63" s="27"/>
+      <c r="Q63" s="34"/>
+      <c r="R63" s="24"/>
       <c r="S63" s="7">
         <v>3.22</v>
       </c>
-      <c r="T63" s="30">
+      <c r="T63" s="33">
         <v>117.033</v>
       </c>
-      <c r="U63" s="27"/>
+      <c r="U63" s="24"/>
       <c r="V63" s="7">
         <v>36.345999999999997</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A64" s="23"/>
-      <c r="B64" s="25"/>
+      <c r="A64" s="20"/>
+      <c r="B64" s="22"/>
       <c r="C64" s="13"/>
       <c r="D64" s="15"/>
       <c r="E64" s="14"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="23"/>
-      <c r="B65" s="25"/>
+      <c r="A65" s="20"/>
+      <c r="B65" s="22"/>
       <c r="C65" s="13"/>
       <c r="D65" s="15"/>
       <c r="E65" s="14"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="23"/>
-      <c r="B66" s="25"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="22"/>
       <c r="C66" s="13"/>
       <c r="D66" s="15"/>
       <c r="E66" s="14"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="23"/>
-      <c r="B67" s="25"/>
+      <c r="A67" s="20"/>
+      <c r="B67" s="22"/>
       <c r="C67" s="13"/>
       <c r="D67" s="15"/>
       <c r="E67" s="14"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="23"/>
-      <c r="B68" s="25"/>
+      <c r="A68" s="20"/>
+      <c r="B68" s="22"/>
       <c r="C68" s="13"/>
       <c r="D68" s="15"/>
       <c r="E68" s="14"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="23"/>
-      <c r="B69" s="25"/>
+      <c r="A69" s="20"/>
+      <c r="B69" s="22"/>
       <c r="C69" s="13"/>
       <c r="D69" s="15"/>
       <c r="E69" s="14"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="23"/>
-      <c r="B70" s="25"/>
+      <c r="A70" s="20"/>
+      <c r="B70" s="22"/>
       <c r="C70" s="13"/>
       <c r="D70" s="15"/>
       <c r="E70" s="14"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="23"/>
-      <c r="B71" s="25"/>
+      <c r="A71" s="20"/>
+      <c r="B71" s="22"/>
       <c r="C71" s="13"/>
       <c r="D71" s="15"/>
       <c r="E71" s="14"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="23"/>
-      <c r="B72" s="25"/>
+      <c r="A72" s="20"/>
+      <c r="B72" s="22"/>
       <c r="C72" s="13"/>
       <c r="D72" s="15"/>
       <c r="E72" s="14"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="23"/>
-      <c r="B73" s="25"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="22"/>
       <c r="C73" s="13"/>
       <c r="D73" s="15"/>
       <c r="E73" s="14"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="23"/>
-      <c r="B74" s="25"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="22"/>
       <c r="C74" s="13"/>
       <c r="D74" s="15"/>
       <c r="E74" s="14"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="23"/>
-      <c r="B75" s="25"/>
+      <c r="A75" s="20"/>
+      <c r="B75" s="22"/>
       <c r="C75" s="13"/>
       <c r="D75" s="15"/>
       <c r="E75" s="14"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="23"/>
-      <c r="B76" s="25"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="13"/>
       <c r="D76" s="15"/>
       <c r="E76" s="14"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="23"/>
-      <c r="B77" s="25"/>
+      <c r="A77" s="20"/>
+      <c r="B77" s="22"/>
       <c r="C77" s="13"/>
       <c r="D77" s="15"/>
       <c r="E77" s="14"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="23"/>
-      <c r="B78" s="25"/>
+      <c r="A78" s="20"/>
+      <c r="B78" s="22"/>
       <c r="C78" s="13"/>
       <c r="D78" s="15"/>
       <c r="E78" s="14"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="23"/>
-      <c r="B79" s="25"/>
+      <c r="A79" s="20"/>
+      <c r="B79" s="22"/>
       <c r="C79" s="13"/>
       <c r="D79" s="15"/>
       <c r="E79" s="14"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="23"/>
-      <c r="B80" s="25"/>
+      <c r="A80" s="20"/>
+      <c r="B80" s="22"/>
       <c r="C80" s="13"/>
       <c r="D80" s="15"/>
       <c r="E80" s="14"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="23"/>
-      <c r="B81" s="25"/>
+      <c r="A81" s="20"/>
+      <c r="B81" s="22"/>
       <c r="C81" s="13"/>
       <c r="D81" s="15"/>
       <c r="E81" s="14"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="23"/>
-      <c r="B82" s="25"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="22"/>
       <c r="C82" s="13"/>
       <c r="D82" s="15"/>
       <c r="E82" s="14"/>
     </row>
     <row r="83" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="23"/>
-      <c r="B83" s="25"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="22"/>
       <c r="C83" s="13"/>
       <c r="D83" s="15"/>
       <c r="E83" s="14"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="23"/>
-      <c r="B84" s="25"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="22"/>
       <c r="C84" s="13"/>
       <c r="D84" s="15"/>
       <c r="E84" s="14"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="23"/>
-      <c r="B85" s="25"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="22"/>
       <c r="C85" s="13"/>
       <c r="D85" s="15"/>
       <c r="E85" s="14"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="23"/>
-      <c r="B86" s="25"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="22"/>
       <c r="C86" s="13"/>
       <c r="D86" s="15"/>
       <c r="E86" s="14"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="23"/>
-      <c r="B87" s="25"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="22"/>
       <c r="C87" s="13"/>
       <c r="D87" s="15"/>
       <c r="E87" s="14"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="23"/>
-      <c r="B88" s="25"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="22"/>
       <c r="C88" s="13"/>
       <c r="D88" s="15"/>
       <c r="E88" s="14"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="23"/>
-      <c r="B89" s="25"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="22"/>
       <c r="C89" s="13"/>
       <c r="D89" s="15"/>
       <c r="E89" s="14"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="23"/>
-      <c r="B90" s="25"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="22"/>
       <c r="C90" s="13"/>
       <c r="D90" s="15"/>
       <c r="E90" s="14"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="23"/>
-      <c r="B91" s="25"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="22"/>
       <c r="C91" s="13"/>
       <c r="D91" s="15"/>
       <c r="E91" s="14"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="23"/>
-      <c r="B92" s="25"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="22"/>
       <c r="C92" s="13"/>
       <c r="D92" s="15"/>
       <c r="E92" s="14"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="23"/>
-      <c r="B93" s="25"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="22"/>
       <c r="C93" s="13"/>
       <c r="D93" s="15"/>
       <c r="E93" s="14"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="23"/>
-      <c r="B94" s="25"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="22"/>
       <c r="C94" s="13"/>
       <c r="D94" s="15"/>
       <c r="E94" s="14"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="23"/>
-      <c r="B95" s="25"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="22"/>
       <c r="C95" s="13"/>
       <c r="D95" s="15"/>
       <c r="E95" s="14"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="23"/>
-      <c r="B96" s="25"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="22"/>
       <c r="C96" s="13"/>
       <c r="D96" s="15"/>
       <c r="E96" s="14"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="23"/>
-      <c r="B97" s="25"/>
+      <c r="A97" s="20"/>
+      <c r="B97" s="22"/>
       <c r="C97" s="13"/>
       <c r="D97" s="15"/>
       <c r="E97" s="14"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="23"/>
-      <c r="B98" s="25"/>
+      <c r="A98" s="20"/>
+      <c r="B98" s="22"/>
       <c r="C98" s="13"/>
       <c r="D98" s="15"/>
       <c r="E98" s="14"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="23"/>
-      <c r="B99" s="25"/>
+      <c r="A99" s="20"/>
+      <c r="B99" s="22"/>
       <c r="C99" s="13"/>
       <c r="D99" s="15"/>
       <c r="E99" s="14"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="23"/>
-      <c r="B100" s="25"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="22"/>
       <c r="C100" s="13"/>
       <c r="D100" s="15"/>
       <c r="E100" s="14"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="23"/>
-      <c r="B101" s="25"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="22"/>
       <c r="C101" s="13"/>
       <c r="D101" s="15"/>
       <c r="E101" s="14"/>
     </row>
     <row r="102" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="23"/>
-      <c r="B102" s="25"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="22"/>
       <c r="C102" s="13"/>
       <c r="D102" s="15"/>
       <c r="E102" s="14"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" s="23"/>
-      <c r="B103" s="25"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="22"/>
       <c r="C103" s="13"/>
       <c r="D103" s="15"/>
       <c r="E103" s="14"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" s="23"/>
-      <c r="B104" s="25"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="22"/>
       <c r="C104" s="13"/>
       <c r="D104" s="15"/>
       <c r="E104" s="14"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" s="23"/>
-      <c r="B105" s="25"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="22"/>
       <c r="C105" s="13"/>
       <c r="D105" s="15"/>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="23"/>
-      <c r="B106" s="25"/>
+      <c r="A106" s="20"/>
+      <c r="B106" s="22"/>
       <c r="C106" s="13"/>
       <c r="D106" s="15"/>
       <c r="E106" s="14"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="23"/>
-      <c r="B107" s="25"/>
+      <c r="A107" s="20"/>
+      <c r="B107" s="22"/>
       <c r="C107" s="13"/>
       <c r="D107" s="15"/>
       <c r="E107" s="14"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="23"/>
-      <c r="B108" s="25"/>
+      <c r="A108" s="20"/>
+      <c r="B108" s="22"/>
       <c r="C108" s="13"/>
       <c r="D108" s="15"/>
       <c r="E108" s="14"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="23"/>
-      <c r="B109" s="25"/>
+      <c r="A109" s="20"/>
+      <c r="B109" s="22"/>
       <c r="C109" s="13"/>
       <c r="D109" s="15"/>
       <c r="E109" s="14"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="23"/>
-      <c r="B110" s="25"/>
+      <c r="A110" s="20"/>
+      <c r="B110" s="22"/>
       <c r="C110" s="13"/>
       <c r="D110" s="15"/>
       <c r="E110" s="14"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" s="23"/>
-      <c r="B111" s="25"/>
+      <c r="A111" s="20"/>
+      <c r="B111" s="22"/>
       <c r="C111" s="13"/>
       <c r="D111" s="15"/>
       <c r="E111" s="14"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="23"/>
-      <c r="B112" s="25"/>
+      <c r="A112" s="20"/>
+      <c r="B112" s="22"/>
       <c r="C112" s="13"/>
       <c r="D112" s="15"/>
       <c r="E112" s="14"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="23"/>
-      <c r="B113" s="25"/>
+      <c r="A113" s="20"/>
+      <c r="B113" s="22"/>
       <c r="C113" s="13"/>
       <c r="D113" s="15"/>
       <c r="E113" s="14"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="23"/>
-      <c r="B114" s="25"/>
+      <c r="A114" s="20"/>
+      <c r="B114" s="22"/>
       <c r="C114" s="13"/>
       <c r="D114" s="15"/>
       <c r="E114" s="14"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="23"/>
-      <c r="B115" s="25"/>
+      <c r="A115" s="20"/>
+      <c r="B115" s="22"/>
       <c r="C115" s="13"/>
       <c r="D115" s="15"/>
       <c r="E115" s="14"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" s="23"/>
-      <c r="B116" s="25"/>
+      <c r="A116" s="20"/>
+      <c r="B116" s="22"/>
       <c r="C116" s="13"/>
       <c r="D116" s="15"/>
       <c r="E116" s="14"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A117" s="23"/>
-      <c r="B117" s="25"/>
+      <c r="A117" s="20"/>
+      <c r="B117" s="22"/>
       <c r="C117" s="13"/>
       <c r="D117" s="15"/>
       <c r="E117" s="14"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A118" s="23"/>
-      <c r="B118" s="25"/>
+      <c r="A118" s="20"/>
+      <c r="B118" s="22"/>
       <c r="C118" s="13"/>
       <c r="D118" s="15"/>
       <c r="E118" s="14"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A119" s="23"/>
-      <c r="B119" s="25"/>
+      <c r="A119" s="20"/>
+      <c r="B119" s="22"/>
       <c r="C119" s="13"/>
       <c r="D119" s="15"/>
       <c r="E119" s="14"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A120" s="23"/>
-      <c r="B120" s="25"/>
+      <c r="A120" s="20"/>
+      <c r="B120" s="22"/>
       <c r="C120" s="13"/>
       <c r="D120" s="15"/>
       <c r="E120" s="14"/>
@@ -10373,229 +10373,340 @@
       <c r="B1487" s="11"/>
     </row>
     <row r="1488" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1488" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1488" s="33"/>
+      <c r="A1488" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1488" s="28"/>
     </row>
     <row r="1489" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1489" s="34"/>
-      <c r="B1489" s="35"/>
+      <c r="A1489" s="29"/>
+      <c r="B1489" s="30"/>
     </row>
     <row r="1490" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1490" s="34"/>
-      <c r="B1490" s="35"/>
+      <c r="A1490" s="29"/>
+      <c r="B1490" s="30"/>
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1491" s="34"/>
-      <c r="B1491" s="35"/>
+      <c r="A1491" s="29"/>
+      <c r="B1491" s="30"/>
     </row>
     <row r="1492" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1492" s="34"/>
-      <c r="B1492" s="35"/>
+      <c r="A1492" s="29"/>
+      <c r="B1492" s="30"/>
     </row>
     <row r="1493" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1493" s="34"/>
-      <c r="B1493" s="35"/>
+      <c r="A1493" s="29"/>
+      <c r="B1493" s="30"/>
     </row>
     <row r="1494" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1494" s="34"/>
-      <c r="B1494" s="35"/>
+      <c r="A1494" s="29"/>
+      <c r="B1494" s="30"/>
     </row>
     <row r="1495" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1495" s="34"/>
-      <c r="B1495" s="35"/>
+      <c r="A1495" s="29"/>
+      <c r="B1495" s="30"/>
     </row>
     <row r="1496" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1496" s="34"/>
-      <c r="B1496" s="35"/>
+      <c r="A1496" s="29"/>
+      <c r="B1496" s="30"/>
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1497" s="34"/>
-      <c r="B1497" s="35"/>
+      <c r="A1497" s="29"/>
+      <c r="B1497" s="30"/>
     </row>
     <row r="1498" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1498" s="34"/>
-      <c r="B1498" s="35"/>
+      <c r="A1498" s="29"/>
+      <c r="B1498" s="30"/>
     </row>
     <row r="1499" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1499" s="34"/>
-      <c r="B1499" s="35"/>
+      <c r="A1499" s="29"/>
+      <c r="B1499" s="30"/>
     </row>
     <row r="1500" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1500" s="34"/>
-      <c r="B1500" s="35"/>
+      <c r="A1500" s="29"/>
+      <c r="B1500" s="30"/>
     </row>
     <row r="1501" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1501" s="34"/>
-      <c r="B1501" s="35"/>
+      <c r="A1501" s="29"/>
+      <c r="B1501" s="30"/>
     </row>
     <row r="1502" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1502" s="34"/>
-      <c r="B1502" s="35"/>
+      <c r="A1502" s="29"/>
+      <c r="B1502" s="30"/>
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1503" s="34"/>
-      <c r="B1503" s="35"/>
+      <c r="A1503" s="29"/>
+      <c r="B1503" s="30"/>
     </row>
     <row r="1504" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1504" s="34"/>
-      <c r="B1504" s="35"/>
+      <c r="A1504" s="29"/>
+      <c r="B1504" s="30"/>
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1505" s="34"/>
-      <c r="B1505" s="35"/>
+      <c r="A1505" s="29"/>
+      <c r="B1505" s="30"/>
     </row>
     <row r="1506" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1506" s="34"/>
-      <c r="B1506" s="35"/>
+      <c r="A1506" s="29"/>
+      <c r="B1506" s="30"/>
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1507" s="34"/>
-      <c r="B1507" s="35"/>
+      <c r="A1507" s="29"/>
+      <c r="B1507" s="30"/>
     </row>
     <row r="1508" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1508" s="34"/>
-      <c r="B1508" s="35"/>
+      <c r="A1508" s="29"/>
+      <c r="B1508" s="30"/>
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1509" s="34"/>
-      <c r="B1509" s="35"/>
+      <c r="A1509" s="29"/>
+      <c r="B1509" s="30"/>
     </row>
     <row r="1510" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1510" s="34"/>
-      <c r="B1510" s="35"/>
+      <c r="A1510" s="29"/>
+      <c r="B1510" s="30"/>
     </row>
     <row r="1511" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1511" s="34"/>
-      <c r="B1511" s="35"/>
+      <c r="A1511" s="29"/>
+      <c r="B1511" s="30"/>
     </row>
     <row r="1512" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1512" s="34"/>
-      <c r="B1512" s="35"/>
+      <c r="A1512" s="29"/>
+      <c r="B1512" s="30"/>
     </row>
     <row r="1513" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1513" s="34"/>
-      <c r="B1513" s="35"/>
+      <c r="A1513" s="29"/>
+      <c r="B1513" s="30"/>
     </row>
     <row r="1514" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1514" s="34"/>
-      <c r="B1514" s="35"/>
+      <c r="A1514" s="29"/>
+      <c r="B1514" s="30"/>
     </row>
     <row r="1515" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1515" s="34"/>
-      <c r="B1515" s="35"/>
+      <c r="A1515" s="29"/>
+      <c r="B1515" s="30"/>
     </row>
     <row r="1516" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1516" s="34"/>
-      <c r="B1516" s="35"/>
+      <c r="A1516" s="29"/>
+      <c r="B1516" s="30"/>
     </row>
     <row r="1517" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1517" s="34"/>
-      <c r="B1517" s="35"/>
+      <c r="A1517" s="29"/>
+      <c r="B1517" s="30"/>
     </row>
     <row r="1518" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1518" s="34"/>
-      <c r="B1518" s="35"/>
+      <c r="A1518" s="29"/>
+      <c r="B1518" s="30"/>
     </row>
     <row r="1519" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1519" s="34"/>
-      <c r="B1519" s="35"/>
+      <c r="A1519" s="29"/>
+      <c r="B1519" s="30"/>
     </row>
     <row r="1520" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1520" s="34"/>
-      <c r="B1520" s="35"/>
+      <c r="A1520" s="29"/>
+      <c r="B1520" s="30"/>
     </row>
     <row r="1521" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1521" s="34"/>
-      <c r="B1521" s="35"/>
+      <c r="A1521" s="29"/>
+      <c r="B1521" s="30"/>
     </row>
     <row r="1522" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1522" s="34"/>
-      <c r="B1522" s="35"/>
+      <c r="A1522" s="29"/>
+      <c r="B1522" s="30"/>
     </row>
     <row r="1523" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1523" s="34"/>
-      <c r="B1523" s="35"/>
+      <c r="A1523" s="29"/>
+      <c r="B1523" s="30"/>
     </row>
     <row r="1524" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1524" s="34"/>
-      <c r="B1524" s="35"/>
+      <c r="A1524" s="29"/>
+      <c r="B1524" s="30"/>
     </row>
     <row r="1525" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1525" s="34"/>
-      <c r="B1525" s="35"/>
+      <c r="A1525" s="29"/>
+      <c r="B1525" s="30"/>
     </row>
     <row r="1526" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1526" s="34"/>
-      <c r="B1526" s="35"/>
+      <c r="A1526" s="29"/>
+      <c r="B1526" s="30"/>
     </row>
     <row r="1527" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1527" s="34"/>
-      <c r="B1527" s="35"/>
+      <c r="A1527" s="29"/>
+      <c r="B1527" s="30"/>
     </row>
     <row r="1528" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1528" s="34"/>
-      <c r="B1528" s="35"/>
+      <c r="A1528" s="29"/>
+      <c r="B1528" s="30"/>
     </row>
     <row r="1529" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1529" s="34"/>
-      <c r="B1529" s="35"/>
+      <c r="A1529" s="29"/>
+      <c r="B1529" s="30"/>
     </row>
     <row r="1530" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1530" s="34"/>
-      <c r="B1530" s="35"/>
+      <c r="A1530" s="29"/>
+      <c r="B1530" s="30"/>
     </row>
     <row r="1531" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1531" s="34"/>
-      <c r="B1531" s="35"/>
+      <c r="A1531" s="29"/>
+      <c r="B1531" s="30"/>
     </row>
     <row r="1532" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1532" s="34"/>
-      <c r="B1532" s="35"/>
+      <c r="A1532" s="29"/>
+      <c r="B1532" s="30"/>
     </row>
     <row r="1533" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1533" s="34"/>
-      <c r="B1533" s="35"/>
+      <c r="A1533" s="29"/>
+      <c r="B1533" s="30"/>
     </row>
     <row r="1534" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1534" s="34"/>
-      <c r="B1534" s="35"/>
+      <c r="A1534" s="29"/>
+      <c r="B1534" s="30"/>
     </row>
     <row r="1535" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1535" s="34"/>
-      <c r="B1535" s="35"/>
+      <c r="A1535" s="29"/>
+      <c r="B1535" s="30"/>
     </row>
     <row r="1536" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1536" s="34"/>
-      <c r="B1536" s="35"/>
+      <c r="A1536" s="29"/>
+      <c r="B1536" s="30"/>
     </row>
     <row r="1537" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1537" s="34"/>
-      <c r="B1537" s="35"/>
+      <c r="A1537" s="29"/>
+      <c r="B1537" s="30"/>
     </row>
     <row r="1538" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1538" s="34"/>
-      <c r="B1538" s="35"/>
+      <c r="A1538" s="29"/>
+      <c r="B1538" s="30"/>
     </row>
     <row r="1539" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1539" s="34"/>
-      <c r="B1539" s="35"/>
+      <c r="A1539" s="29"/>
+      <c r="B1539" s="30"/>
     </row>
     <row r="1540" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1540" s="34"/>
-      <c r="B1540" s="35"/>
+      <c r="A1540" s="29"/>
+      <c r="B1540" s="30"/>
     </row>
     <row r="1541" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1541" s="36"/>
-      <c r="B1541" s="37"/>
+      <c r="A1541" s="31"/>
+      <c r="B1541" s="32"/>
     </row>
     <row r="1542" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1542" s="31"/>
-      <c r="B1542" s="27"/>
+      <c r="A1542" s="23"/>
+      <c r="B1542" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="135">
+    <mergeCell ref="C2:E22"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="P30:R30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="P31:R31"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="P37:R37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="P46:R46"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="P47:R47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="P45:R45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="T41:U41"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="P56:R56"/>
+    <mergeCell ref="T56:U56"/>
+    <mergeCell ref="P51:R51"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="P53:R53"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="P48:R48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="P49:R49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="P50:R50"/>
+    <mergeCell ref="T50:U50"/>
     <mergeCell ref="C23:E30"/>
     <mergeCell ref="C31:E44"/>
     <mergeCell ref="C45:E63"/>
@@ -10620,117 +10731,6 @@
     <mergeCell ref="T54:U54"/>
     <mergeCell ref="P55:R55"/>
     <mergeCell ref="T55:U55"/>
-    <mergeCell ref="P56:R56"/>
-    <mergeCell ref="T56:U56"/>
-    <mergeCell ref="P51:R51"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="P52:R52"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="P53:R53"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="P48:R48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="P49:R49"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="P50:R50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="P46:R46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="P47:R47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="P45:R45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="T41:U41"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="P40:R40"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="P36:R36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="P37:R37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="P32:R32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="P31:R31"/>
-    <mergeCell ref="P30:R30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="P28:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="C2:E22"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="P14:R14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
